--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="736">
   <si>
     <t>code</t>
   </si>
@@ -304,6 +304,12 @@
     <t>21502</t>
   </si>
   <si>
+    <t>21064</t>
+  </si>
+  <si>
+    <t>Initiative Clinton pour l'accès à la santé</t>
+  </si>
+  <si>
     <t>22000</t>
   </si>
   <si>
@@ -391,7 +397,7 @@
     <t>21027</t>
   </si>
   <si>
-    <t>ITF Améliorer la sécurité humaine</t>
+    <t>Fonds international d’affectation spéciale pour le déminage et l’assistance aux victimes des mines</t>
   </si>
   <si>
     <t>21040</t>
@@ -469,6 +475,9 @@
     <t>23501</t>
   </si>
   <si>
+    <t>Sociétés nationales de la Croix-Rouge et du Croissant-Rouge</t>
+  </si>
+  <si>
     <t>21030</t>
   </si>
   <si>
@@ -499,6 +508,12 @@
     <t>Alliance pour les villes</t>
   </si>
   <si>
+    <t>31006</t>
+  </si>
+  <si>
+    <t>Coalition pour les innovations en matière de préparation</t>
+  </si>
+  <si>
     <t>30016</t>
   </si>
   <si>
@@ -775,6 +790,12 @@
     <t>Programme commun des Nations Unies sur le VIH/SIDA</t>
   </si>
   <si>
+    <t>41320</t>
+  </si>
+  <si>
+    <t>Banque de Technologies en faveur des Pays les Moins Avancés</t>
+  </si>
+  <si>
     <t>41305</t>
   </si>
   <si>
@@ -1036,6 +1057,9 @@
     <t>41319</t>
   </si>
   <si>
+    <t>Organisation mondiale du tourisme</t>
+  </si>
+  <si>
     <t>42000</t>
   </si>
   <si>
@@ -1201,7 +1225,7 @@
     <t>46008</t>
   </si>
   <si>
-    <t>Société andine de développement</t>
+    <t>Banque de développement de l'Amérique latine</t>
   </si>
   <si>
     <t>46004</t>
@@ -1219,6 +1243,9 @@
     <t>46026</t>
   </si>
   <si>
+    <t>Banque Asiatique d’Investissement dans les Infrastructures</t>
+  </si>
+  <si>
     <t>46006</t>
   </si>
   <si>
@@ -1627,6 +1654,27 @@
     <t>Organisation internationale des migrations</t>
   </si>
   <si>
+    <t>41149</t>
+  </si>
+  <si>
+    <t>Bureau de la coordination des activités de développement des Nations Unies</t>
+  </si>
+  <si>
+    <t>41150</t>
+  </si>
+  <si>
+    <t>Institut des Nations Unies pour la recherche sur le désarmement</t>
+  </si>
+  <si>
+    <t>46027</t>
+  </si>
+  <si>
+    <t>Fonds financier pour le développement du bassin fluvial de la Plata</t>
+  </si>
+  <si>
+    <t>47400</t>
+  </si>
+  <si>
     <t>47046</t>
   </si>
   <si>
@@ -1855,6 +1903,21 @@
     <t>Agence internationale pour les energies renouvelables</t>
   </si>
   <si>
+    <t>47146</t>
+  </si>
+  <si>
+    <t>47147</t>
+  </si>
+  <si>
+    <t>Facilité internationale de financement pour l'éducation</t>
+  </si>
+  <si>
+    <t>47148</t>
+  </si>
+  <si>
+    <t>Organisation mondiale de la santé animale</t>
+  </si>
+  <si>
     <t>50000</t>
   </si>
   <si>
@@ -2056,9 +2119,6 @@
     <t>61001</t>
   </si>
   <si>
-    <t>Banque privée dans le pays donneur</t>
-  </si>
-  <si>
     <t>61002</t>
   </si>
   <si>
@@ -2068,13 +2128,25 @@
     <t>61003</t>
   </si>
   <si>
-    <t>Investisseur privé dans le pays donneur</t>
-  </si>
-  <si>
     <t>61004</t>
   </si>
   <si>
-    <t>Autre entité non-bancaire dans le pays donneur</t>
+    <t>61005</t>
+  </si>
+  <si>
+    <t>61006</t>
+  </si>
+  <si>
+    <t>61007</t>
+  </si>
+  <si>
+    <t>61008</t>
+  </si>
+  <si>
+    <t>61009</t>
+  </si>
+  <si>
+    <t>61010</t>
   </si>
   <si>
     <t>62000</t>
@@ -2086,19 +2158,31 @@
     <t>62001</t>
   </si>
   <si>
-    <t>Banque privée dans le pays bénéficiaire</t>
-  </si>
-  <si>
     <t>62002</t>
   </si>
   <si>
-    <t>Co-entreprise dans le pays bénéficiaire</t>
-  </si>
-  <si>
     <t>62003</t>
   </si>
   <si>
-    <t>Autre entité non-bancaire dans le pays bénéficiaire</t>
+    <t>62004</t>
+  </si>
+  <si>
+    <t>62005</t>
+  </si>
+  <si>
+    <t>62006</t>
+  </si>
+  <si>
+    <t>62007</t>
+  </si>
+  <si>
+    <t>62008</t>
+  </si>
+  <si>
+    <t>62009</t>
+  </si>
+  <si>
+    <t>62010</t>
   </si>
   <si>
     <t>63000</t>
@@ -2110,13 +2194,31 @@
     <t>63001</t>
   </si>
   <si>
-    <t>Banque privée d'un pays tiers</t>
-  </si>
-  <si>
     <t>63002</t>
   </si>
   <si>
-    <t>Secteur privé non-bancaire dans un pays tiers</t>
+    <t>63003</t>
+  </si>
+  <si>
+    <t>63004</t>
+  </si>
+  <si>
+    <t>63005</t>
+  </si>
+  <si>
+    <t>63006</t>
+  </si>
+  <si>
+    <t>63007</t>
+  </si>
+  <si>
+    <t>63008</t>
+  </si>
+  <si>
+    <t>63009</t>
+  </si>
+  <si>
+    <t>63010</t>
   </si>
   <si>
     <t>90000</t>
@@ -2451,7 +2553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F360"/>
+  <dimension ref="A1:F391"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3180,13 +3282,16 @@
       <c r="A68" t="s">
         <v>128</v>
       </c>
+      <c r="B68" t="s">
+        <v>129</v>
+      </c>
       <c r="F68" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F69" t="s">
         <v>8</v>
@@ -3194,9 +3299,6 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>130</v>
-      </c>
-      <c r="B70" t="s">
         <v>131</v>
       </c>
       <c r="F70" t="s">
@@ -3306,16 +3408,19 @@
       <c r="A80" t="s">
         <v>150</v>
       </c>
+      <c r="B80" t="s">
+        <v>151</v>
+      </c>
       <c r="F80" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F81" t="s">
         <v>8</v>
@@ -3323,10 +3428,10 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F82" t="s">
         <v>8</v>
@@ -3334,10 +3439,10 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F83" t="s">
         <v>8</v>
@@ -3345,10 +3450,10 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B84" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F84" t="s">
         <v>8</v>
@@ -3356,10 +3461,10 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B85" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F85" t="s">
         <v>8</v>
@@ -3367,10 +3472,10 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F86" t="s">
         <v>8</v>
@@ -3378,10 +3483,10 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B87" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F87" t="s">
         <v>8</v>
@@ -3389,10 +3494,10 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F88" t="s">
         <v>8</v>
@@ -3400,10 +3505,10 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F89" t="s">
         <v>8</v>
@@ -3411,10 +3516,10 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F90" t="s">
         <v>8</v>
@@ -3422,10 +3527,10 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B91" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F91" t="s">
         <v>8</v>
@@ -3433,10 +3538,10 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B92" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F92" t="s">
         <v>8</v>
@@ -3444,10 +3549,10 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B93" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F93" t="s">
         <v>8</v>
@@ -3455,10 +3560,10 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B94" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F94" t="s">
         <v>8</v>
@@ -3466,10 +3571,10 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B95" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F95" t="s">
         <v>8</v>
@@ -3477,10 +3582,10 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F96" t="s">
         <v>8</v>
@@ -3488,10 +3593,10 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B97" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F97" t="s">
         <v>8</v>
@@ -3499,10 +3604,10 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B98" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F98" t="s">
         <v>8</v>
@@ -3510,10 +3615,10 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B99" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F99" t="s">
         <v>8</v>
@@ -3521,10 +3626,10 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B100" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F100" t="s">
         <v>8</v>
@@ -3532,10 +3637,10 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B101" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F101" t="s">
         <v>8</v>
@@ -3543,10 +3648,10 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B102" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F102" t="s">
         <v>8</v>
@@ -3554,10 +3659,10 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B103" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F103" t="s">
         <v>8</v>
@@ -3565,10 +3670,10 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B104" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F104" t="s">
         <v>8</v>
@@ -3576,10 +3681,10 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B105" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F105" t="s">
         <v>8</v>
@@ -3587,10 +3692,10 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F106" t="s">
         <v>8</v>
@@ -3598,10 +3703,10 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B107" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F107" t="s">
         <v>8</v>
@@ -3609,10 +3714,10 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B108" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" t="s">
         <v>8</v>
@@ -3620,10 +3725,10 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B109" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F109" t="s">
         <v>8</v>
@@ -3631,10 +3736,10 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B110" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F110" t="s">
         <v>8</v>
@@ -3642,10 +3747,10 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B111" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F111" t="s">
         <v>8</v>
@@ -3653,10 +3758,10 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B112" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F112" t="s">
         <v>8</v>
@@ -3664,10 +3769,10 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B113" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F113" t="s">
         <v>8</v>
@@ -3675,10 +3780,10 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B114" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F114" t="s">
         <v>8</v>
@@ -3686,10 +3791,10 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B115" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F115" t="s">
         <v>8</v>
@@ -3697,10 +3802,10 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B116" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F116" t="s">
         <v>8</v>
@@ -3708,10 +3813,10 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B117" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
         <v>8</v>
@@ -3719,10 +3824,10 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B118" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F118" t="s">
         <v>8</v>
@@ -3730,10 +3835,10 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B119" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F119" t="s">
         <v>8</v>
@@ -3741,10 +3846,10 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B120" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F120" t="s">
         <v>8</v>
@@ -3752,10 +3857,10 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B121" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F121" t="s">
         <v>8</v>
@@ -3763,10 +3868,10 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F122" t="s">
         <v>8</v>
@@ -3774,10 +3879,10 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B123" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F123" t="s">
         <v>8</v>
@@ -3785,10 +3890,10 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B124" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F124" t="s">
         <v>8</v>
@@ -3796,10 +3901,10 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B125" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F125" t="s">
         <v>8</v>
@@ -3807,10 +3912,10 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B126" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F126" t="s">
         <v>8</v>
@@ -3818,10 +3923,10 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B127" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F127" t="s">
         <v>8</v>
@@ -3829,10 +3934,10 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B128" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F128" t="s">
         <v>8</v>
@@ -3840,10 +3945,10 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B129" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F129" t="s">
         <v>8</v>
@@ -3851,10 +3956,10 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B130" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F130" t="s">
         <v>8</v>
@@ -3862,10 +3967,10 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B131" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F131" t="s">
         <v>8</v>
@@ -3873,10 +3978,10 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B132" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F132" t="s">
         <v>8</v>
@@ -3884,10 +3989,10 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B133" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F133" t="s">
         <v>8</v>
@@ -3895,10 +4000,10 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B134" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F134" t="s">
         <v>8</v>
@@ -3906,10 +4011,10 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B135" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F135" t="s">
         <v>8</v>
@@ -3917,10 +4022,10 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F136" t="s">
         <v>8</v>
@@ -3928,10 +4033,10 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F137" t="s">
         <v>8</v>
@@ -3939,10 +4044,10 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F138" t="s">
         <v>8</v>
@@ -3950,10 +4055,10 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B139" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F139" t="s">
         <v>8</v>
@@ -3961,10 +4066,10 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B140" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F140" t="s">
         <v>8</v>
@@ -3972,10 +4077,10 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B141" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F141" t="s">
         <v>8</v>
@@ -3983,10 +4088,10 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B142" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F142" t="s">
         <v>8</v>
@@ -3994,10 +4099,10 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B143" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F143" t="s">
         <v>8</v>
@@ -4005,10 +4110,10 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B144" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F144" t="s">
         <v>8</v>
@@ -4016,10 +4121,10 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B145" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F145" t="s">
         <v>8</v>
@@ -4027,10 +4132,10 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B146" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F146" t="s">
         <v>8</v>
@@ -4038,10 +4143,10 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B147" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F147" t="s">
         <v>8</v>
@@ -4049,10 +4154,10 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B148" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F148" t="s">
         <v>8</v>
@@ -4060,10 +4165,10 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B149" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F149" t="s">
         <v>8</v>
@@ -4071,10 +4176,10 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F150" t="s">
         <v>8</v>
@@ -4082,10 +4187,10 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B151" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F151" t="s">
         <v>8</v>
@@ -4093,10 +4198,10 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B152" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F152" t="s">
         <v>8</v>
@@ -4104,10 +4209,10 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B153" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F153" t="s">
         <v>8</v>
@@ -4115,10 +4220,10 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B154" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F154" t="s">
         <v>8</v>
@@ -4126,10 +4231,10 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B155" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F155" t="s">
         <v>8</v>
@@ -4137,10 +4242,10 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B156" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F156" t="s">
         <v>8</v>
@@ -4148,10 +4253,10 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B157" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F157" t="s">
         <v>8</v>
@@ -4159,7 +4264,10 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>305</v>
+        <v>306</v>
+      </c>
+      <c r="B158" t="s">
+        <v>307</v>
       </c>
       <c r="F158" t="s">
         <v>8</v>
@@ -4167,10 +4275,10 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B159" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F159" t="s">
         <v>8</v>
@@ -4178,10 +4286,10 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B160" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F160" t="s">
         <v>8</v>
@@ -4189,10 +4297,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>310</v>
-      </c>
-      <c r="B161" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F161" t="s">
         <v>8</v>
@@ -4200,10 +4305,10 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B162" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F162" t="s">
         <v>8</v>
@@ -4211,10 +4316,10 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B163" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F163" t="s">
         <v>8</v>
@@ -4222,10 +4327,10 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B164" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F164" t="s">
         <v>8</v>
@@ -4233,10 +4338,10 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B165" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F165" t="s">
         <v>8</v>
@@ -4244,10 +4349,10 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B166" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F166" t="s">
         <v>8</v>
@@ -4255,10 +4360,10 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B167" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F167" t="s">
         <v>8</v>
@@ -4266,10 +4371,10 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B168" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F168" t="s">
         <v>8</v>
@@ -4277,10 +4382,10 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B169" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F169" t="s">
         <v>8</v>
@@ -4288,7 +4393,10 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>328</v>
+        <v>329</v>
+      </c>
+      <c r="B170" t="s">
+        <v>330</v>
       </c>
       <c r="F170" t="s">
         <v>8</v>
@@ -4296,10 +4404,10 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B171" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F171" t="s">
         <v>8</v>
@@ -4307,10 +4415,10 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B172" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F172" t="s">
         <v>8</v>
@@ -4318,10 +4426,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>333</v>
-      </c>
-      <c r="B173" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F173" t="s">
         <v>8</v>
@@ -4329,10 +4434,10 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B174" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F174" t="s">
         <v>8</v>
@@ -4340,10 +4445,10 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B175" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F175" t="s">
         <v>8</v>
@@ -4351,7 +4456,10 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>339</v>
+        <v>340</v>
+      </c>
+      <c r="B176" t="s">
+        <v>341</v>
       </c>
       <c r="F176" t="s">
         <v>8</v>
@@ -4359,10 +4467,10 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B177" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F177" t="s">
         <v>8</v>
@@ -4370,10 +4478,10 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B178" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F178" t="s">
         <v>8</v>
@@ -4381,10 +4489,10 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B179" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F179" t="s">
         <v>8</v>
@@ -4392,10 +4500,10 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B180" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F180" t="s">
         <v>8</v>
@@ -4403,10 +4511,10 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B181" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F181" t="s">
         <v>8</v>
@@ -4414,10 +4522,10 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B182" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F182" t="s">
         <v>8</v>
@@ -4425,10 +4533,10 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B183" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F183" t="s">
         <v>8</v>
@@ -4436,10 +4544,10 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B184" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F184" t="s">
         <v>8</v>
@@ -4447,10 +4555,10 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B185" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F185" t="s">
         <v>8</v>
@@ -4458,10 +4566,10 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B186" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F186" t="s">
         <v>8</v>
@@ -4469,10 +4577,10 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B187" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F187" t="s">
         <v>8</v>
@@ -4480,10 +4588,10 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B188" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F188" t="s">
         <v>8</v>
@@ -4491,10 +4599,10 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B189" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F189" t="s">
         <v>8</v>
@@ -4502,10 +4610,10 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B190" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F190" t="s">
         <v>8</v>
@@ -4513,10 +4621,10 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B191" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F191" t="s">
         <v>8</v>
@@ -4524,10 +4632,10 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B192" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F192" t="s">
         <v>8</v>
@@ -4535,10 +4643,10 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B193" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F193" t="s">
         <v>8</v>
@@ -4546,10 +4654,10 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B194" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F194" t="s">
         <v>8</v>
@@ -4557,10 +4665,10 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B195" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F195" t="s">
         <v>8</v>
@@ -4568,10 +4676,10 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B196" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F196" t="s">
         <v>8</v>
@@ -4579,10 +4687,10 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B197" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F197" t="s">
         <v>8</v>
@@ -4590,10 +4698,10 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B198" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F198" t="s">
         <v>8</v>
@@ -4601,10 +4709,10 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B199" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F199" t="s">
         <v>8</v>
@@ -4612,10 +4720,10 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B200" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F200" t="s">
         <v>8</v>
@@ -4623,10 +4731,10 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B201" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F201" t="s">
         <v>8</v>
@@ -4634,10 +4742,10 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B202" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F202" t="s">
         <v>8</v>
@@ -4645,10 +4753,10 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B203" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F203" t="s">
         <v>8</v>
@@ -4656,10 +4764,10 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B204" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F204" t="s">
         <v>8</v>
@@ -4667,10 +4775,10 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B205" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F205" t="s">
         <v>8</v>
@@ -4678,10 +4786,10 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B206" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F206" t="s">
         <v>8</v>
@@ -4689,7 +4797,10 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>400</v>
+        <v>402</v>
+      </c>
+      <c r="B207" t="s">
+        <v>403</v>
       </c>
       <c r="F207" t="s">
         <v>8</v>
@@ -4697,10 +4808,10 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B208" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F208" t="s">
         <v>8</v>
@@ -4708,10 +4819,10 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B209" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F209" t="s">
         <v>8</v>
@@ -4719,10 +4830,10 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B210" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F210" t="s">
         <v>8</v>
@@ -4730,10 +4841,10 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B211" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F211" t="s">
         <v>8</v>
@@ -4741,10 +4852,10 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B212" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F212" t="s">
         <v>8</v>
@@ -4752,10 +4863,10 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B213" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F213" t="s">
         <v>8</v>
@@ -4763,10 +4874,10 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B214" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F214" t="s">
         <v>8</v>
@@ -4774,10 +4885,10 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B215" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F215" t="s">
         <v>8</v>
@@ -4785,10 +4896,10 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B216" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F216" t="s">
         <v>8</v>
@@ -4796,10 +4907,10 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B217" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F217" t="s">
         <v>8</v>
@@ -4807,10 +4918,10 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B218" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F218" t="s">
         <v>8</v>
@@ -4818,10 +4929,10 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B219" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F219" t="s">
         <v>8</v>
@@ -4829,10 +4940,10 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B220" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F220" t="s">
         <v>8</v>
@@ -4840,10 +4951,10 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B221" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F221" t="s">
         <v>8</v>
@@ -4851,10 +4962,10 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B222" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F222" t="s">
         <v>8</v>
@@ -4862,10 +4973,10 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B223" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F223" t="s">
         <v>8</v>
@@ -4873,10 +4984,10 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B224" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F224" t="s">
         <v>8</v>
@@ -4884,10 +4995,10 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B225" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F225" t="s">
         <v>8</v>
@@ -4895,10 +5006,10 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B226" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F226" t="s">
         <v>8</v>
@@ -4906,10 +5017,10 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B227" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F227" t="s">
         <v>8</v>
@@ -4917,10 +5028,10 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B228" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F228" t="s">
         <v>8</v>
@@ -4928,10 +5039,10 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B229" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F229" t="s">
         <v>8</v>
@@ -4939,10 +5050,10 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B230" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F230" t="s">
         <v>8</v>
@@ -4950,10 +5061,10 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B231" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F231" t="s">
         <v>8</v>
@@ -4961,10 +5072,10 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B232" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F232" t="s">
         <v>8</v>
@@ -4972,10 +5083,10 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B233" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F233" t="s">
         <v>8</v>
@@ -4983,10 +5094,10 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B234" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F234" t="s">
         <v>8</v>
@@ -4994,10 +5105,10 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B235" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F235" t="s">
         <v>8</v>
@@ -5005,10 +5116,10 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B236" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F236" t="s">
         <v>8</v>
@@ -5016,7 +5127,10 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>459</v>
+        <v>462</v>
+      </c>
+      <c r="B237" t="s">
+        <v>463</v>
       </c>
       <c r="F237" t="s">
         <v>8</v>
@@ -5024,10 +5138,10 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B238" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F238" t="s">
         <v>8</v>
@@ -5035,10 +5149,10 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B239" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F239" t="s">
         <v>8</v>
@@ -5046,10 +5160,7 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>464</v>
-      </c>
-      <c r="B240" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F240" t="s">
         <v>8</v>
@@ -5057,10 +5168,10 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B241" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F241" t="s">
         <v>8</v>
@@ -5068,10 +5179,10 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B242" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F242" t="s">
         <v>8</v>
@@ -5079,10 +5190,10 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B243" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F243" t="s">
         <v>8</v>
@@ -5090,10 +5201,10 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B244" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F244" t="s">
         <v>8</v>
@@ -5101,10 +5212,10 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B245" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F245" t="s">
         <v>8</v>
@@ -5112,10 +5223,10 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B246" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F246" t="s">
         <v>8</v>
@@ -5123,10 +5234,10 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B247" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F247" t="s">
         <v>8</v>
@@ -5134,10 +5245,10 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B248" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="F248" t="s">
         <v>8</v>
@@ -5145,10 +5256,10 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B249" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F249" t="s">
         <v>8</v>
@@ -5156,10 +5267,10 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B250" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F250" t="s">
         <v>8</v>
@@ -5167,10 +5278,10 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B251" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F251" t="s">
         <v>8</v>
@@ -5178,10 +5289,10 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B252" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F252" t="s">
         <v>8</v>
@@ -5189,7 +5300,10 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>490</v>
+        <v>493</v>
+      </c>
+      <c r="B253" t="s">
+        <v>494</v>
       </c>
       <c r="F253" t="s">
         <v>8</v>
@@ -5197,10 +5311,10 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B254" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F254" t="s">
         <v>8</v>
@@ -5208,10 +5322,10 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B255" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F255" t="s">
         <v>8</v>
@@ -5219,10 +5333,7 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>495</v>
-      </c>
-      <c r="B256" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F256" t="s">
         <v>8</v>
@@ -5230,7 +5341,10 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>497</v>
+        <v>500</v>
+      </c>
+      <c r="B257" t="s">
+        <v>501</v>
       </c>
       <c r="F257" t="s">
         <v>8</v>
@@ -5238,10 +5352,10 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B258" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F258" t="s">
         <v>8</v>
@@ -5249,10 +5363,10 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B259" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F259" t="s">
         <v>8</v>
@@ -5260,10 +5374,7 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>502</v>
-      </c>
-      <c r="B260" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F260" t="s">
         <v>8</v>
@@ -5271,10 +5382,10 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B261" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F261" t="s">
         <v>8</v>
@@ -5282,7 +5393,10 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>506</v>
+        <v>509</v>
+      </c>
+      <c r="B262" t="s">
+        <v>510</v>
       </c>
       <c r="F262" t="s">
         <v>8</v>
@@ -5290,10 +5404,10 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B263" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F263" t="s">
         <v>8</v>
@@ -5301,10 +5415,10 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B264" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F264" t="s">
         <v>8</v>
@@ -5312,10 +5426,7 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>511</v>
-      </c>
-      <c r="B265" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F265" t="s">
         <v>8</v>
@@ -5323,10 +5434,10 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B266" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F266" t="s">
         <v>8</v>
@@ -5334,10 +5445,10 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B267" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F267" t="s">
         <v>8</v>
@@ -5345,10 +5456,10 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B268" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F268" t="s">
         <v>8</v>
@@ -5356,10 +5467,10 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B269" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F269" t="s">
         <v>8</v>
@@ -5367,10 +5478,10 @@
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B270" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F270" t="s">
         <v>8</v>
@@ -5378,10 +5489,10 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B271" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F271" t="s">
         <v>8</v>
@@ -5389,10 +5500,10 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B272" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F272" t="s">
         <v>8</v>
@@ -5400,10 +5511,10 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B273" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F273" t="s">
         <v>8</v>
@@ -5411,10 +5522,10 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B274" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F274" t="s">
         <v>8</v>
@@ -5422,10 +5533,10 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B275" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F275" t="s">
         <v>8</v>
@@ -5433,10 +5544,10 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B276" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F276" t="s">
         <v>8</v>
@@ -5444,10 +5555,10 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B277" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F277" t="s">
         <v>8</v>
@@ -5455,10 +5566,10 @@
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B278" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F278" t="s">
         <v>8</v>
@@ -5466,10 +5577,10 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B279" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F279" t="s">
         <v>8</v>
@@ -5477,10 +5588,10 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B280" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F280" t="s">
         <v>8</v>
@@ -5488,10 +5599,10 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B281" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F281" t="s">
         <v>8</v>
@@ -5499,10 +5610,10 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B282" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F282" t="s">
         <v>8</v>
@@ -5510,10 +5621,10 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B283" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F283" t="s">
         <v>8</v>
@@ -5521,10 +5632,7 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>549</v>
-      </c>
-      <c r="B284" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F284" t="s">
         <v>8</v>
@@ -5532,10 +5640,10 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B285" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F285" t="s">
         <v>8</v>
@@ -5543,10 +5651,10 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B286" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F286" t="s">
         <v>8</v>
@@ -5554,10 +5662,10 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B287" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F287" t="s">
         <v>8</v>
@@ -5565,10 +5673,10 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B288" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F288" t="s">
         <v>8</v>
@@ -5576,10 +5684,10 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B289" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F289" t="s">
         <v>8</v>
@@ -5587,10 +5695,10 @@
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B290" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F290" t="s">
         <v>8</v>
@@ -5598,10 +5706,10 @@
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B291" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F291" t="s">
         <v>8</v>
@@ -5609,10 +5717,10 @@
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B292" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F292" t="s">
         <v>8</v>
@@ -5620,10 +5728,10 @@
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B293" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F293" t="s">
         <v>8</v>
@@ -5631,10 +5739,10 @@
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B294" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F294" t="s">
         <v>8</v>
@@ -5642,10 +5750,10 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B295" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F295" t="s">
         <v>8</v>
@@ -5653,10 +5761,10 @@
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B296" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F296" t="s">
         <v>8</v>
@@ -5664,10 +5772,10 @@
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B297" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F297" t="s">
         <v>8</v>
@@ -5675,10 +5783,10 @@
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B298" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F298" t="s">
         <v>8</v>
@@ -5686,10 +5794,10 @@
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B299" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F299" t="s">
         <v>8</v>
@@ -5697,10 +5805,10 @@
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B300" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F300" t="s">
         <v>8</v>
@@ -5708,10 +5816,10 @@
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B301" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F301" t="s">
         <v>8</v>
@@ -5719,10 +5827,10 @@
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B302" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F302" t="s">
         <v>8</v>
@@ -5730,10 +5838,10 @@
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B303" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F303" t="s">
         <v>8</v>
@@ -5741,10 +5849,10 @@
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B304" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F304" t="s">
         <v>8</v>
@@ -5752,10 +5860,10 @@
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B305" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F305" t="s">
         <v>8</v>
@@ -5763,10 +5871,10 @@
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B306" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F306" t="s">
         <v>8</v>
@@ -5774,10 +5882,10 @@
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B307" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F307" t="s">
         <v>8</v>
@@ -5785,10 +5893,10 @@
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B308" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F308" t="s">
         <v>8</v>
@@ -5796,10 +5904,10 @@
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B309" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="F309" t="s">
         <v>8</v>
@@ -5807,10 +5915,10 @@
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B310" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F310" t="s">
         <v>8</v>
@@ -5818,10 +5926,10 @@
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B311" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="F311" t="s">
         <v>8</v>
@@ -5829,10 +5937,10 @@
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B312" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F312" t="s">
         <v>8</v>
@@ -5840,10 +5948,10 @@
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B313" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F313" t="s">
         <v>8</v>
@@ -5851,10 +5959,10 @@
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B314" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F314" t="s">
         <v>8</v>
@@ -5862,10 +5970,10 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B315" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F315" t="s">
         <v>8</v>
@@ -5873,21 +5981,21 @@
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B316" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F316" t="s">
-        <v>615</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B317" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F317" t="s">
         <v>8</v>
@@ -5895,10 +6003,10 @@
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B318" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F318" t="s">
         <v>8</v>
@@ -5906,10 +6014,10 @@
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B319" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F319" t="s">
         <v>8</v>
@@ -5917,10 +6025,10 @@
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B320" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F320" t="s">
         <v>8</v>
@@ -5928,10 +6036,10 @@
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B321" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F321" t="s">
         <v>8</v>
@@ -5939,10 +6047,10 @@
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B322" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F322" t="s">
         <v>8</v>
@@ -5950,9 +6058,6 @@
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>628</v>
-      </c>
-      <c r="B323" t="s">
         <v>629</v>
       </c>
       <c r="F323" t="s">
@@ -5989,15 +6094,15 @@
         <v>635</v>
       </c>
       <c r="F326" t="s">
-        <v>8</v>
+        <v>636</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B327" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F327" t="s">
         <v>8</v>
@@ -6005,10 +6110,10 @@
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B328" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F328" t="s">
         <v>8</v>
@@ -6016,10 +6121,10 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B329" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F329" t="s">
         <v>8</v>
@@ -6027,10 +6132,10 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B330" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F330" t="s">
         <v>8</v>
@@ -6038,10 +6143,10 @@
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B331" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F331" t="s">
         <v>8</v>
@@ -6049,10 +6154,10 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B332" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F332" t="s">
         <v>8</v>
@@ -6060,10 +6165,10 @@
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B333" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F333" t="s">
         <v>8</v>
@@ -6071,10 +6176,10 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B334" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F334" t="s">
         <v>8</v>
@@ -6082,10 +6187,10 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B335" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F335" t="s">
         <v>8</v>
@@ -6093,10 +6198,10 @@
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B336" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F336" t="s">
         <v>8</v>
@@ -6104,10 +6209,10 @@
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B337" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F337" t="s">
         <v>8</v>
@@ -6115,10 +6220,10 @@
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B338" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F338" t="s">
         <v>8</v>
@@ -6126,10 +6231,10 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B339" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F339" t="s">
         <v>8</v>
@@ -6137,10 +6242,10 @@
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B340" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F340" t="s">
         <v>8</v>
@@ -6148,10 +6253,10 @@
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B341" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F341" t="s">
         <v>8</v>
@@ -6159,10 +6264,10 @@
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B342" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F342" t="s">
         <v>8</v>
@@ -6170,10 +6275,10 @@
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B343" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F343" t="s">
         <v>8</v>
@@ -6181,10 +6286,10 @@
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B344" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F344" t="s">
         <v>8</v>
@@ -6192,10 +6297,10 @@
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B345" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F345" t="s">
         <v>8</v>
@@ -6203,21 +6308,21 @@
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B346" t="s">
-        <v>614</v>
+        <v>676</v>
       </c>
       <c r="F346" t="s">
-        <v>615</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B347" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F347" t="s">
         <v>8</v>
@@ -6225,10 +6330,10 @@
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B348" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F348" t="s">
         <v>8</v>
@@ -6236,10 +6341,10 @@
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B349" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F349" t="s">
         <v>8</v>
@@ -6247,10 +6352,10 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B350" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F350" t="s">
         <v>8</v>
@@ -6258,10 +6363,10 @@
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B351" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F351" t="s">
         <v>8</v>
@@ -6269,10 +6374,10 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B352" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F352" t="s">
         <v>8</v>
@@ -6280,10 +6385,10 @@
     </row>
     <row r="353" spans="1:6">
       <c r="A353" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B353" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F353" t="s">
         <v>8</v>
@@ -6291,10 +6396,10 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B354" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F354" t="s">
         <v>8</v>
@@ -6302,10 +6407,10 @@
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B355" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F355" t="s">
         <v>8</v>
@@ -6313,21 +6418,21 @@
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B356" t="s">
-        <v>694</v>
+        <v>635</v>
       </c>
       <c r="F356" t="s">
-        <v>8</v>
+        <v>636</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B357" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F357" t="s">
         <v>8</v>
@@ -6335,10 +6440,10 @@
     </row>
     <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B358" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F358" t="s">
         <v>8</v>
@@ -6346,9 +6451,6 @@
     </row>
     <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>699</v>
-      </c>
-      <c r="B359" t="s">
         <v>700</v>
       </c>
       <c r="F359" t="s">
@@ -6360,9 +6462,266 @@
         <v>701</v>
       </c>
       <c r="B360" t="s">
-        <v>614</v>
+        <v>702</v>
       </c>
       <c r="F360" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" t="s">
+        <v>703</v>
+      </c>
+      <c r="F361" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" t="s">
+        <v>704</v>
+      </c>
+      <c r="F362" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" t="s">
+        <v>705</v>
+      </c>
+      <c r="F363" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" t="s">
+        <v>706</v>
+      </c>
+      <c r="F364" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" t="s">
+        <v>707</v>
+      </c>
+      <c r="F365" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" t="s">
+        <v>708</v>
+      </c>
+      <c r="F366" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" t="s">
+        <v>709</v>
+      </c>
+      <c r="F367" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" t="s">
+        <v>710</v>
+      </c>
+      <c r="F368" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" t="s">
+        <v>711</v>
+      </c>
+      <c r="B369" t="s">
+        <v>712</v>
+      </c>
+      <c r="F369" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" t="s">
+        <v>713</v>
+      </c>
+      <c r="F370" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" t="s">
+        <v>714</v>
+      </c>
+      <c r="F371" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" t="s">
+        <v>715</v>
+      </c>
+      <c r="F372" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" t="s">
+        <v>716</v>
+      </c>
+      <c r="F373" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" t="s">
+        <v>717</v>
+      </c>
+      <c r="F374" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" t="s">
+        <v>718</v>
+      </c>
+      <c r="F375" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" t="s">
+        <v>719</v>
+      </c>
+      <c r="F376" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" t="s">
+        <v>720</v>
+      </c>
+      <c r="F377" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" t="s">
+        <v>721</v>
+      </c>
+      <c r="F378" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" t="s">
+        <v>722</v>
+      </c>
+      <c r="F379" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" t="s">
+        <v>723</v>
+      </c>
+      <c r="B380" t="s">
+        <v>724</v>
+      </c>
+      <c r="F380" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" t="s">
+        <v>725</v>
+      </c>
+      <c r="F381" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" t="s">
+        <v>726</v>
+      </c>
+      <c r="F382" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" t="s">
+        <v>727</v>
+      </c>
+      <c r="F383" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" t="s">
+        <v>728</v>
+      </c>
+      <c r="F384" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" t="s">
+        <v>729</v>
+      </c>
+      <c r="F385" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
+      <c r="A386" t="s">
+        <v>730</v>
+      </c>
+      <c r="F386" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
+      <c r="A387" t="s">
+        <v>731</v>
+      </c>
+      <c r="F387" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6">
+      <c r="A388" t="s">
+        <v>732</v>
+      </c>
+      <c r="F388" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
+      <c r="A389" t="s">
+        <v>733</v>
+      </c>
+      <c r="F389" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
+      <c r="A390" t="s">
+        <v>734</v>
+      </c>
+      <c r="F390" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6">
+      <c r="A391" t="s">
+        <v>735</v>
+      </c>
+      <c r="B391" t="s">
+        <v>635</v>
+      </c>
+      <c r="F391" t="s">
         <v>8</v>
       </c>
     </row>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="748">
   <si>
     <t>code</t>
   </si>
@@ -32,6 +32,42 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>public-database</t>
+  </si>
+  <si>
+    <t>budget_alignment_guidance</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>10000</t>
@@ -2553,10 +2589,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F391"/>
+  <dimension ref="A1:MD391"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:342">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2575,4154 +2611,5162 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ED1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="FZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="GZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="HZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="ID1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="II1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="IZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="JZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KT1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KU1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KV1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KW1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KX1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KY1" t="s">
+        <v>7</v>
+      </c>
+      <c r="KZ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LA1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LP1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LQ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LR1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="LT1" t="s">
+        <v>8</v>
+      </c>
+      <c r="LU1" t="s">
+        <v>9</v>
+      </c>
+      <c r="LV1" t="s">
+        <v>10</v>
+      </c>
+      <c r="LW1" t="s">
+        <v>11</v>
+      </c>
+      <c r="LX1" t="s">
+        <v>12</v>
+      </c>
+      <c r="LY1" t="s">
+        <v>13</v>
+      </c>
+      <c r="LZ1" t="s">
+        <v>14</v>
+      </c>
+      <c r="MA1" t="s">
+        <v>15</v>
+      </c>
+      <c r="MB1" t="s">
+        <v>16</v>
+      </c>
+      <c r="MC1" t="s">
+        <v>17</v>
+      </c>
+      <c r="MD1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:342">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:342">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:342">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:342">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:342">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:342">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:342">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:342">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:342">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:342">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:342">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:342">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:342">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:342">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:342">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F16" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F18" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F29" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F30" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F35" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F36" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F44" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F46" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F48" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F52" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F54" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F55" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F56" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F57" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F58" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F59" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="F62" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F63" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F64" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F65" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B66" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F66" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B67" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F68" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F69" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F70" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B71" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F71" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="F72" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F73" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B74" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="F74" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F75" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="B76" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="F76" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B77" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F77" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F78" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B79" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="F79" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="F80" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F82" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B83" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F83" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="B84" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F84" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B85" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F85" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B86" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="F86" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B87" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F87" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B88" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F88" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B89" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F89" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B90" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F90" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B91" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F91" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B92" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F92" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B93" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F93" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B94" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F94" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B95" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F95" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F96" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B97" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B99" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B100" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F100" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B101" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="B102" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B103" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F103" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B104" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B105" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F105" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="B106" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F106" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B107" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F107" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B108" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B109" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B110" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B111" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B112" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F112" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B113" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F113" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B114" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F114" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B115" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F115" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B116" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F116" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B117" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F117" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B118" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="F118" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B119" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="F119" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B120" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F120" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B121" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="F121" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B122" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="F122" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B123" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="F123" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B124" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="F124" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B125" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="F125" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B126" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="F126" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B127" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="F127" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B128" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="F128" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B129" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="F129" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B130" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="F130" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B131" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F131" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B132" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F132" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B133" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="F133" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B134" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F134" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B135" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F135" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B136" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="F136" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B137" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="F137" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B138" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="F138" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B139" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="F139" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B140" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="F140" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B141" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F141" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B142" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="F142" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B143" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="F143" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B144" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="F144" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B145" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="F145" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B146" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F146" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B147" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="F147" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B148" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="F148" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B149" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="F149" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B150" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="F150" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B151" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="F151" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B152" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="F152" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B153" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="F153" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B154" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F154" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B155" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="F155" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B156" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F156" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B157" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="F157" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B158" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="F158" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B159" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F159" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B160" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="F160" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="F161" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B162" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="F162" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B163" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="F163" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B164" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="F164" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B165" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="F165" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B166" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F166" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B167" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="F167" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B168" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="F168" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B169" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="F169" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B170" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="F170" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B171" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="F171" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B172" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F172" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F173" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B174" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="F174" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B175" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F175" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B176" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F176" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B177" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="F177" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B178" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="F178" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B179" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F179" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B180" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="F180" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B181" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F181" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B182" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F182" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B183" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="F183" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B184" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F184" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B185" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F185" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B186" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="F186" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B187" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F187" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B188" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="F188" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B189" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="F189" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B190" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F190" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B191" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F191" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B192" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F192" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="B193" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="F193" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B194" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="F194" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B195" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F195" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B196" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F196" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F197" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B198" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F198" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B199" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F199" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B200" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F200" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B201" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F201" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B202" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F202" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B203" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F203" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B204" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F204" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B205" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F205" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B206" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F206" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B207" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F207" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B208" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="F208" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B209" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F209" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B210" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="F210" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="B211" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="F211" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B212" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F212" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="B213" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="F213" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B214" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="F214" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B215" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F215" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B216" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="F216" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="B217" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="F217" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B218" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="F218" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B219" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="F219" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B220" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="F220" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B221" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="F221" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="B222" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="F222" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="B223" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F223" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B224" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="F224" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B225" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="F225" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B226" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="F226" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B227" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="F227" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B228" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F228" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B229" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="F229" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B230" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="F230" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B231" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F231" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B232" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="F232" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B233" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="F233" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B234" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="F234" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B235" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="F235" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B236" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="F236" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="B237" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="F237" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B238" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="F238" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="B239" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="F239" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="F240" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B241" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="F241" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B242" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="F242" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B243" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="F243" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="B244" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="F244" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="B245" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="F245" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B246" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="F246" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B247" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="F247" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B248" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="F248" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B249" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="F249" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="B250" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="F250" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B251" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="F251" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B252" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="F252" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B253" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="F253" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="B254" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="F254" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B255" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F255" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="F256" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B257" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="F257" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B258" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F258" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="B259" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F259" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="F260" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="B261" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="F261" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B262" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="F262" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="B263" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F263" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="B264" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="F264" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="F265" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B266" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="F266" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B267" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="F267" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B268" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="F268" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B269" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="F269" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="B270" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="F270" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="B271" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="F271" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="B272" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="F272" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="B273" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="F273" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="B274" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="F274" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B275" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="F275" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="B276" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="F276" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="B277" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="F277" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="B278" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F278" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B279" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="F279" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B280" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="F280" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="B281" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="F281" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B282" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="F282" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B283" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="F283" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="F284" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="B285" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F285" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="B286" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="F286" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B287" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="F287" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B288" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="F288" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B289" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="F289" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B290" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="F290" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B291" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="F291" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B292" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="F292" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="B293" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="F293" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B294" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F294" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B295" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="F295" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B296" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="F296" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B297" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="F297" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="B298" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="F298" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B299" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="F299" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="B300" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="F300" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B301" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="F301" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="B302" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="F302" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="B303" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="F303" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="B304" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="F304" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="B305" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="F305" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="B306" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="F306" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="B307" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="F307" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="B308" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="F308" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="B309" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="F309" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="B310" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="F310" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="B311" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="F311" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="B312" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="F312" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="B313" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="F313" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="B314" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="F314" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="B315" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="F315" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="B316" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="F316" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="B317" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="F317" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="B318" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="F318" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="B319" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="F319" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="B320" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="F320" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="B321" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F321" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="B322" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="F322" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="F323" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="B324" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="F324" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B325" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="F325" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="B326" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="F326" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="B327" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="F327" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="B328" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="F328" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="B329" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F329" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="B330" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="F330" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="B331" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="F331" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="B332" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="F332" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="B333" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="F333" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="B334" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="F334" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="B335" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="F335" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="B336" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="F336" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="B337" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="F337" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="B338" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="F338" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="B339" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="F339" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="B340" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="F340" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="B341" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="F341" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="B342" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="F342" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="B343" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="F343" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="B344" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="F344" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="B345" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="F345" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="B346" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="F346" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="B347" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="F347" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="B348" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="F348" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="B349" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="F349" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="B350" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F350" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="B351" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="F351" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="B352" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="F352" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="B353" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="F353" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="B354" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="F354" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="B355" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="F355" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="B356" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="F356" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="B357" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="F357" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="B358" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="F358" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="F359" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="B360" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="F360" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="F361" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="F362" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F363" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="F364" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="365" spans="1:6">
       <c r="A365" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="F365" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="F366" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="F367" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="368" spans="1:6">
       <c r="A368" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="F368" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="369" spans="1:6">
       <c r="A369" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="B369" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="F369" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="370" spans="1:6">
       <c r="A370" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F370" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="371" spans="1:6">
       <c r="A371" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="F371" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="372" spans="1:6">
       <c r="A372" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="F372" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="373" spans="1:6">
       <c r="A373" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="F373" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="F374" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="375" spans="1:6">
       <c r="A375" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="F375" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="376" spans="1:6">
       <c r="A376" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="F376" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="377" spans="1:6">
       <c r="A377" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F377" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="378" spans="1:6">
       <c r="A378" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="F378" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="379" spans="1:6">
       <c r="A379" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="F379" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="380" spans="1:6">
       <c r="A380" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="B380" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="F380" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="381" spans="1:6">
       <c r="A381" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="F381" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="382" spans="1:6">
       <c r="A382" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="F382" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="383" spans="1:6">
       <c r="A383" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="F383" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="384" spans="1:6">
       <c r="A384" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="F384" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="385" spans="1:6">
       <c r="A385" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="F385" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="386" spans="1:6">
       <c r="A386" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="F386" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="387" spans="1:6">
       <c r="A387" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="F387" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="F388" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="389" spans="1:6">
       <c r="A389" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="F389" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="390" spans="1:6">
       <c r="A390" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="F390" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="391" spans="1:6">
       <c r="A391" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="B391" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="F391" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>iso-alpha-3-code</t>
   </si>
   <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>sub-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
     <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>10000</t>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
   </si>
   <si>
     <t>10000</t>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>10000</t>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>10000</t>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
     <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
   </si>
   <si>
     <t>10000</t>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>10000</t>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -43,31 +43,31 @@
     <t>iso-alpha-3-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-code</t>
   </si>
   <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>10000</t>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="736">
   <si>
     <t>code</t>
   </si>
@@ -32,42 +32,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>public-database</t>
-  </si>
-  <si>
-    <t>budget_alignment_guidance</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>10000</t>
@@ -2589,10 +2553,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:MD391"/>
+  <dimension ref="A1:F391"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:342">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2611,5162 +2575,4154 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="DZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ED1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ER1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ES1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ET1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="EZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="FZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="GZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="HZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="ID1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="II1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="IZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="JZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KU1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KV1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KW1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KX1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KY1" t="s">
-        <v>7</v>
-      </c>
-      <c r="KZ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LA1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LC1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LE1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LF1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LG1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LI1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LJ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LK1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LM1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LN1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LO1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LQ1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LR1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LS1" t="s">
-        <v>7</v>
-      </c>
-      <c r="LT1" t="s">
-        <v>8</v>
-      </c>
-      <c r="LU1" t="s">
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="LV1" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="LW1" t="s">
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="LX1" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="LY1" t="s">
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="LZ1" t="s">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="MA1" t="s">
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="MB1" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="MC1" t="s">
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="MD1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:342">
-      <c r="A2" t="s">
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:342">
-      <c r="A3" t="s">
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:342">
-      <c r="A4" t="s">
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:342">
-      <c r="A5" t="s">
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:342">
-      <c r="A6" t="s">
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:342">
-      <c r="A7" t="s">
+      <c r="B14" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:342">
-      <c r="A8" t="s">
+      <c r="B15" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>32</v>
       </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:342">
-      <c r="A9" t="s">
+      <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:342">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:342">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:342">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:342">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:342">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:342">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:342">
-      <c r="A16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B64" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F64" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F65" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="F72" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B75" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F76" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B77" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F80" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B81" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B82" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B83" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F86" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F91" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B93" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B94" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B95" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B96" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B97" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B98" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B99" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B100" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B101" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B102" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B103" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F103" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B105" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F105" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B106" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B107" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B108" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B109" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F109" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B110" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B111" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B112" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F112" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B113" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B114" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F114" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B115" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F115" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B116" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B117" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B118" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="F118" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B119" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B120" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F120" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B121" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B122" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="F122" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B123" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B124" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F124" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="B125" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F125" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B126" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="F126" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B127" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F127" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B128" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="F128" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B129" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="F129" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B130" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="F130" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B131" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="F131" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B132" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="F132" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B133" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="F133" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B134" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F134" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B135" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="F135" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B136" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F136" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B137" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="F137" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B138" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="F138" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B139" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="F139" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B140" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F140" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B141" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="F141" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="B142" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="F142" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B143" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="F143" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="B144" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="F144" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="B145" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="F145" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B146" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F146" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B147" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="F147" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B148" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="F148" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B149" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="F149" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="B150" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="F150" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B151" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="F151" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B152" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="F152" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B153" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="F153" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B154" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="F154" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B155" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="F155" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B156" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F156" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B157" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="F157" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B158" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="F158" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B159" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="F159" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B160" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="F160" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="F161" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B162" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="F162" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="B163" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="F163" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="B164" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="F164" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B165" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="F165" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="B166" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="F166" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B167" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="F167" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B168" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="F168" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="B169" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="F169" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B170" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="F170" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B171" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="F171" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B172" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="F172" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="F173" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B174" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="F174" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="B175" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="F175" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B176" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="F176" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B177" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="F177" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="B178" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="F178" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B179" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="F179" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B180" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="F180" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B181" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="F181" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B182" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="F182" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="B183" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="F183" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B184" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="F184" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B185" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="F185" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B186" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="F186" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B187" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="F187" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B188" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="F188" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B189" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="F189" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="B190" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="F190" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B191" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="F191" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="B192" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="F192" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="B193" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="F193" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="B194" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="F194" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B195" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="F195" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="B196" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="F196" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B197" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="F197" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="B198" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="F198" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="B199" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="F199" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="B200" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="F200" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="B201" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="F201" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="B202" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F202" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B203" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="F203" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="B204" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="F204" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="B205" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="F205" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="B206" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="F206" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="B207" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="F207" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="B208" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="F208" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B209" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="F209" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="B210" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="F210" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="B211" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="F211" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B212" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="F212" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B213" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="F213" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B214" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="F214" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B215" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="F215" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="B216" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="F216" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B217" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="F217" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B218" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="F218" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B219" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="F219" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B220" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="F220" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B221" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="F221" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="B222" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="F222" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="B223" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="F223" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="B224" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="F224" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="B225" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="F225" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B226" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F226" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B227" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F227" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B228" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="F228" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B229" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="F229" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B230" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="F230" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B231" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="F231" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B232" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="F232" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="B233" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="F233" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="B234" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="F234" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B235" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="F235" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="B236" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="F236" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B237" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="F237" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B238" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="F238" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B239" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="F239" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="F240" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B241" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="F241" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="B242" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="F242" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B243" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="F243" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B244" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="F244" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="B245" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="F245" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="B246" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="F246" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B247" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="F247" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="B248" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="F248" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B249" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="F249" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="B250" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="F250" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B251" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="F251" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B252" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="F252" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B253" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="F253" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="B254" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="F254" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B255" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="F255" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="F256" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="B257" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="F257" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="B258" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="F258" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="B259" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="F259" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="F260" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="B261" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="F261" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="B262" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="F262" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="B263" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="F263" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="B264" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="F264" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="F265" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="B266" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="F266" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="B267" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="F267" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B268" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="F268" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B269" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="F269" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="B270" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="F270" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B271" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="F271" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="B272" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="F272" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="B273" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="F273" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B274" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="F274" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="B275" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="F275" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="B276" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="F276" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="B277" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="F277" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="B278" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="F278" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="B279" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="F279" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B280" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="F280" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="B281" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="F281" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="B282" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="F282" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="B283" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="F283" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="F284" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="B285" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="F285" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B286" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="F286" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B287" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="F287" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="B288" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="F288" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B289" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="F289" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="B290" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="F290" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="B291" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="F291" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="B292" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="F292" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="B293" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="F293" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="B294" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="F294" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="B295" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="F295" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="B296" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="F296" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="B297" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="F297" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B298" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="F298" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="B299" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="F299" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B300" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="F300" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B301" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="F301" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="B302" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="F302" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="B303" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="F303" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B304" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="F304" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B305" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="F305" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B306" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="F306" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B307" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="F307" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B308" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="F308" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B309" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="F309" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="B310" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="F310" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="B311" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="F311" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B312" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="F312" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="B313" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="F313" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B314" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="F314" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B315" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="F315" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="B316" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="F316" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="B317" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="F317" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B318" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="F318" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="B319" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="F319" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="B320" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="F320" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="B321" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="F321" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="B322" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="F322" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="F323" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="B324" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="F324" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="B325" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="F325" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="B326" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="F326" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="B327" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="F327" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="B328" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="F328" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="B329" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="F329" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="B330" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="F330" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="B331" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="F331" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="B332" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="F332" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="B333" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="F333" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="B334" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="F334" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B335" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="F335" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="B336" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="F336" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="B337" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="F337" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="B338" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="F338" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="B339" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="F339" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="B340" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="F340" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="B341" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="F341" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="B342" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="F342" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="B343" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="F343" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B344" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="F344" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="B345" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="F345" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="B346" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="F346" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="B347" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="F347" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="B348" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="F348" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="B349" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="F349" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="B350" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="F350" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="B351" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="F351" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="B352" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="F352" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="B353" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="F353" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="B354" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="F354" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="B355" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="F355" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="B356" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="F356" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="B357" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="F357" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="B358" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="F358" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="F359" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="B360" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="F360" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="F361" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="F362" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F363" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="F364" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:6">
       <c r="A365" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="F365" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="F366" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="F367" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:6">
       <c r="A368" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="F368" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:6">
       <c r="A369" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="B369" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="F369" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="370" spans="1:6">
       <c r="A370" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="F370" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:6">
       <c r="A371" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="F371" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:6">
       <c r="A372" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="F372" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="373" spans="1:6">
       <c r="A373" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="F373" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="F374" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="375" spans="1:6">
       <c r="A375" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="F375" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:6">
       <c r="A376" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="F376" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:6">
       <c r="A377" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="F377" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="378" spans="1:6">
       <c r="A378" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="F378" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="379" spans="1:6">
       <c r="A379" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="F379" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:6">
       <c r="A380" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="B380" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="F380" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:6">
       <c r="A381" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="F381" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="382" spans="1:6">
       <c r="A382" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="F382" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:6">
       <c r="A383" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="F383" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="384" spans="1:6">
       <c r="A384" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="F384" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="385" spans="1:6">
       <c r="A385" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="F385" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:6">
       <c r="A386" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="F386" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="387" spans="1:6">
       <c r="A387" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="F387" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="F388" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:6">
       <c r="A389" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="F389" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:6">
       <c r="A390" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="F390" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:6">
       <c r="A391" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="B391" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="F391" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -14,21 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="733">
   <si>
     <t>code</t>
   </si>
   <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>url</t>
   </si>
   <si>
     <t>status</t>
@@ -2553,10 +2544,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F391"/>
+  <dimension ref="A1:C391"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2566,4163 +2557,4154 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>25</v>
       </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="F13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
         <v>28</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="F14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>31</v>
       </c>
-      <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="B17" t="s">
         <v>32</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="F16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
         <v>34</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="F17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>36</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="F18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>38</v>
       </c>
-      <c r="F19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+      <c r="B21" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>40</v>
       </c>
-      <c r="F20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+      <c r="B22" t="s">
         <v>41</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>42</v>
       </c>
-      <c r="F21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>44</v>
       </c>
-      <c r="F22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>45</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
         <v>46</v>
       </c>
-      <c r="F23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>47</v>
       </c>
-      <c r="F24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+      <c r="B26" t="s">
         <v>48</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>49</v>
       </c>
-      <c r="F25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
+      <c r="B27" t="s">
         <v>50</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>51</v>
       </c>
-      <c r="F26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="B28" t="s">
         <v>52</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>53</v>
       </c>
-      <c r="F27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
+      <c r="B29" t="s">
         <v>54</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>55</v>
       </c>
-      <c r="F28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+      <c r="B30" t="s">
         <v>56</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>57</v>
       </c>
-      <c r="F29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="B31" t="s">
         <v>58</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>59</v>
       </c>
-      <c r="F30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
+      <c r="B32" t="s">
         <v>60</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>61</v>
       </c>
-      <c r="F31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
+      <c r="B33" t="s">
         <v>62</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>63</v>
       </c>
-      <c r="F32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
+      <c r="B34" t="s">
         <v>64</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>65</v>
       </c>
-      <c r="F33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
+      <c r="B35" t="s">
         <v>66</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>67</v>
       </c>
-      <c r="F34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
+      <c r="B36" t="s">
         <v>68</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>69</v>
       </c>
-      <c r="F35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
+      <c r="B37" t="s">
         <v>70</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>71</v>
       </c>
-      <c r="F36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>72</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>73</v>
       </c>
-      <c r="F37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+      <c r="B40" t="s">
         <v>74</v>
       </c>
-      <c r="F38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>75</v>
       </c>
-      <c r="F39" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
+      <c r="B41" t="s">
         <v>76</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>77</v>
       </c>
-      <c r="F40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
+      <c r="B42" t="s">
         <v>78</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>79</v>
       </c>
-      <c r="F41" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>80</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>81</v>
       </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
+      <c r="B45" t="s">
         <v>82</v>
       </c>
-      <c r="F43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>83</v>
       </c>
-      <c r="F44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
+      <c r="B46" t="s">
         <v>84</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>85</v>
       </c>
-      <c r="F45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>86</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B48" t="s">
         <v>87</v>
       </c>
-      <c r="F46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>88</v>
       </c>
-      <c r="F47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
+      <c r="B49" t="s">
         <v>89</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>90</v>
       </c>
-      <c r="F48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
+      <c r="B50" t="s">
         <v>91</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>92</v>
       </c>
-      <c r="F49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>93</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B52" t="s">
         <v>94</v>
       </c>
-      <c r="F50" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>95</v>
       </c>
-      <c r="F51" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
+      <c r="B53" t="s">
         <v>96</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>97</v>
       </c>
-      <c r="F52" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
+      <c r="B54" t="s">
         <v>98</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
         <v>99</v>
       </c>
-      <c r="F53" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
+      <c r="B55" t="s">
         <v>100</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
         <v>101</v>
       </c>
-      <c r="F54" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
+      <c r="B56" t="s">
         <v>102</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>103</v>
       </c>
-      <c r="F55" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" t="s">
+      <c r="B57" t="s">
         <v>104</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
         <v>105</v>
       </c>
-      <c r="F56" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
+      <c r="B58" t="s">
         <v>106</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
         <v>107</v>
       </c>
-      <c r="F57" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
+      <c r="B59" t="s">
         <v>108</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
         <v>109</v>
       </c>
-      <c r="F58" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
+      <c r="B60" t="s">
         <v>110</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
         <v>111</v>
       </c>
-      <c r="F59" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
+      <c r="B61" t="s">
         <v>112</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
         <v>113</v>
       </c>
-      <c r="F60" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
+      <c r="B62" t="s">
         <v>114</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
         <v>115</v>
       </c>
-      <c r="F61" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" t="s">
+      <c r="B63" t="s">
         <v>116</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
         <v>117</v>
       </c>
-      <c r="F62" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
+      <c r="B64" t="s">
         <v>118</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
         <v>119</v>
       </c>
-      <c r="F63" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" t="s">
+      <c r="B65" t="s">
         <v>120</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
         <v>121</v>
       </c>
-      <c r="F64" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
+      <c r="B66" t="s">
         <v>122</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
         <v>123</v>
       </c>
-      <c r="F65" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
+      <c r="B67" t="s">
         <v>124</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
         <v>125</v>
       </c>
-      <c r="F66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
+      <c r="B68" t="s">
         <v>126</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
         <v>127</v>
       </c>
-      <c r="F67" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
         <v>128</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
         <v>129</v>
       </c>
-      <c r="F68" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
+      <c r="B71" t="s">
         <v>130</v>
       </c>
-      <c r="F69" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
         <v>131</v>
       </c>
-      <c r="F70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
+      <c r="B72" t="s">
         <v>132</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
         <v>133</v>
       </c>
-      <c r="F71" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
+      <c r="B73" t="s">
         <v>134</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>135</v>
       </c>
-      <c r="F72" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
+      <c r="B74" t="s">
         <v>136</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
         <v>137</v>
       </c>
-      <c r="F73" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
+      <c r="B75" t="s">
         <v>138</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
         <v>139</v>
       </c>
-      <c r="F74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
+      <c r="B76" t="s">
         <v>140</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
         <v>141</v>
       </c>
-      <c r="F75" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
+      <c r="B77" t="s">
         <v>142</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
         <v>143</v>
       </c>
-      <c r="F76" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
+      <c r="B78" t="s">
         <v>144</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
         <v>145</v>
       </c>
-      <c r="F77" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
+      <c r="B79" t="s">
         <v>146</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
         <v>147</v>
       </c>
-      <c r="F78" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
+      <c r="B80" t="s">
         <v>148</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
         <v>149</v>
       </c>
-      <c r="F79" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
+      <c r="B81" t="s">
         <v>150</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
         <v>151</v>
       </c>
-      <c r="F80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" t="s">
+      <c r="B82" t="s">
         <v>152</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
         <v>153</v>
       </c>
-      <c r="F81" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82" t="s">
+      <c r="B83" t="s">
         <v>154</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
         <v>155</v>
       </c>
-      <c r="F82" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83" t="s">
+      <c r="B84" t="s">
         <v>156</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
         <v>157</v>
       </c>
-      <c r="F83" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84" t="s">
+      <c r="B85" t="s">
         <v>158</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
         <v>159</v>
       </c>
-      <c r="F84" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" t="s">
+      <c r="B86" t="s">
         <v>160</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
         <v>161</v>
       </c>
-      <c r="F85" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" t="s">
+      <c r="B87" t="s">
         <v>162</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
         <v>163</v>
       </c>
-      <c r="F86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" t="s">
+      <c r="B88" t="s">
         <v>164</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
         <v>165</v>
       </c>
-      <c r="F87" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88" t="s">
+      <c r="B89" t="s">
         <v>166</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
         <v>167</v>
       </c>
-      <c r="F88" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89" t="s">
+      <c r="B90" t="s">
         <v>168</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
         <v>169</v>
       </c>
-      <c r="F89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" t="s">
+      <c r="B91" t="s">
         <v>170</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
         <v>171</v>
       </c>
-      <c r="F90" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" t="s">
+      <c r="B92" t="s">
         <v>172</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
         <v>173</v>
       </c>
-      <c r="F91" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" t="s">
+      <c r="B93" t="s">
         <v>174</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
         <v>175</v>
       </c>
-      <c r="F92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93" t="s">
+      <c r="B94" t="s">
         <v>176</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
         <v>177</v>
       </c>
-      <c r="F93" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94" t="s">
+      <c r="B95" t="s">
         <v>178</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
         <v>179</v>
       </c>
-      <c r="F94" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95" t="s">
+      <c r="B96" t="s">
         <v>180</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
         <v>181</v>
       </c>
-      <c r="F95" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" t="s">
+      <c r="B97" t="s">
         <v>182</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
         <v>183</v>
       </c>
-      <c r="F96" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97" t="s">
+      <c r="B98" t="s">
         <v>184</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
         <v>185</v>
       </c>
-      <c r="F97" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" t="s">
+      <c r="B99" t="s">
         <v>186</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
         <v>187</v>
       </c>
-      <c r="F98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99" t="s">
+      <c r="B100" t="s">
         <v>188</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
         <v>189</v>
       </c>
-      <c r="F99" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100" t="s">
+      <c r="B101" t="s">
         <v>190</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
         <v>191</v>
       </c>
-      <c r="F100" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101" t="s">
+      <c r="B102" t="s">
         <v>192</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
         <v>193</v>
       </c>
-      <c r="F101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102" t="s">
+      <c r="B103" t="s">
         <v>194</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
         <v>195</v>
       </c>
-      <c r="F102" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103" t="s">
+      <c r="B104" t="s">
         <v>196</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
         <v>197</v>
       </c>
-      <c r="F103" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104" t="s">
+      <c r="B105" t="s">
         <v>198</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
         <v>199</v>
       </c>
-      <c r="F104" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105" t="s">
+      <c r="B106" t="s">
         <v>200</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
         <v>201</v>
       </c>
-      <c r="F105" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106" t="s">
+      <c r="B107" t="s">
         <v>202</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
         <v>203</v>
       </c>
-      <c r="F106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107" t="s">
+      <c r="B108" t="s">
         <v>204</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
         <v>205</v>
       </c>
-      <c r="F107" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108" t="s">
+      <c r="B109" t="s">
         <v>206</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
         <v>207</v>
       </c>
-      <c r="F108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109" t="s">
+      <c r="B110" t="s">
         <v>208</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
         <v>209</v>
       </c>
-      <c r="F109" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" t="s">
+      <c r="B111" t="s">
         <v>210</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
         <v>211</v>
       </c>
-      <c r="F110" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111" t="s">
+      <c r="B112" t="s">
         <v>212</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
         <v>213</v>
       </c>
-      <c r="F111" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112" t="s">
+      <c r="B113" t="s">
         <v>214</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
         <v>215</v>
       </c>
-      <c r="F112" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113" t="s">
+      <c r="B114" t="s">
         <v>216</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
         <v>217</v>
       </c>
-      <c r="F113" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" t="s">
+      <c r="B115" t="s">
         <v>218</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
         <v>219</v>
       </c>
-      <c r="F114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115" t="s">
+      <c r="B116" t="s">
         <v>220</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
         <v>221</v>
       </c>
-      <c r="F115" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116" t="s">
+      <c r="B117" t="s">
         <v>222</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
         <v>223</v>
       </c>
-      <c r="F116" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" t="s">
+      <c r="B118" t="s">
         <v>224</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
         <v>225</v>
       </c>
-      <c r="F117" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118" t="s">
+      <c r="B119" t="s">
         <v>226</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
         <v>227</v>
       </c>
-      <c r="F118" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119" t="s">
+      <c r="B120" t="s">
         <v>228</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
         <v>229</v>
       </c>
-      <c r="F119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120" t="s">
+      <c r="B121" t="s">
         <v>230</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C121" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
         <v>231</v>
       </c>
-      <c r="F120" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121" t="s">
+      <c r="B122" t="s">
         <v>232</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
         <v>233</v>
       </c>
-      <c r="F121" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" t="s">
+      <c r="B123" t="s">
         <v>234</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
         <v>235</v>
       </c>
-      <c r="F122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123" t="s">
+      <c r="B124" t="s">
         <v>236</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C124" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
         <v>237</v>
       </c>
-      <c r="F123" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124" t="s">
+      <c r="B125" t="s">
         <v>238</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
         <v>239</v>
       </c>
-      <c r="F124" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
+      <c r="B126" t="s">
         <v>240</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
         <v>241</v>
       </c>
-      <c r="F125" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126" t="s">
+      <c r="B127" t="s">
         <v>242</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
         <v>243</v>
       </c>
-      <c r="F126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" t="s">
+      <c r="B128" t="s">
         <v>244</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
         <v>245</v>
       </c>
-      <c r="F127" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" t="s">
+      <c r="B129" t="s">
         <v>246</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
         <v>247</v>
       </c>
-      <c r="F128" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" t="s">
+      <c r="B130" t="s">
         <v>248</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
         <v>249</v>
       </c>
-      <c r="F129" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130" t="s">
+      <c r="B131" t="s">
         <v>250</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
         <v>251</v>
       </c>
-      <c r="F130" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131" t="s">
+      <c r="B132" t="s">
         <v>252</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
         <v>253</v>
       </c>
-      <c r="F131" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132" t="s">
+      <c r="B133" t="s">
         <v>254</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
         <v>255</v>
       </c>
-      <c r="F132" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" t="s">
+      <c r="B134" t="s">
         <v>256</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
         <v>257</v>
       </c>
-      <c r="F133" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" t="s">
+      <c r="B135" t="s">
         <v>258</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C135" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
         <v>259</v>
       </c>
-      <c r="F134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135" t="s">
+      <c r="B136" t="s">
         <v>260</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C136" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
         <v>261</v>
       </c>
-      <c r="F135" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136" t="s">
+      <c r="B137" t="s">
         <v>262</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C137" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
         <v>263</v>
       </c>
-      <c r="F136" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137" t="s">
+      <c r="B138" t="s">
         <v>264</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
         <v>265</v>
       </c>
-      <c r="F137" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138" t="s">
+      <c r="B139" t="s">
         <v>266</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C139" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
         <v>267</v>
       </c>
-      <c r="F138" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139" t="s">
+      <c r="B140" t="s">
         <v>268</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C140" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
         <v>269</v>
       </c>
-      <c r="F139" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140" t="s">
+      <c r="B141" t="s">
         <v>270</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C141" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
         <v>271</v>
       </c>
-      <c r="F140" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141" t="s">
+      <c r="B142" t="s">
         <v>272</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C142" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
         <v>273</v>
       </c>
-      <c r="F141" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142" t="s">
+      <c r="B143" t="s">
         <v>274</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
         <v>275</v>
       </c>
-      <c r="F142" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143" t="s">
+      <c r="B144" t="s">
         <v>276</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C144" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
         <v>277</v>
       </c>
-      <c r="F143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144" t="s">
+      <c r="B145" t="s">
         <v>278</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C145" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
         <v>279</v>
       </c>
-      <c r="F144" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145" t="s">
+      <c r="B146" t="s">
         <v>280</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
         <v>281</v>
       </c>
-      <c r="F145" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146" t="s">
+      <c r="B147" t="s">
         <v>282</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C147" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
         <v>283</v>
       </c>
-      <c r="F146" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" t="s">
+      <c r="B148" t="s">
         <v>284</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
         <v>285</v>
       </c>
-      <c r="F147" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" t="s">
+      <c r="B149" t="s">
         <v>286</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C149" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
         <v>287</v>
       </c>
-      <c r="F148" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149" t="s">
+      <c r="B150" t="s">
         <v>288</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C150" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
         <v>289</v>
       </c>
-      <c r="F149" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150" t="s">
+      <c r="B151" t="s">
         <v>290</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C151" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
         <v>291</v>
       </c>
-      <c r="F150" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151" t="s">
+      <c r="B152" t="s">
         <v>292</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C152" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
         <v>293</v>
       </c>
-      <c r="F151" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152" t="s">
+      <c r="B153" t="s">
         <v>294</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C153" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
         <v>295</v>
       </c>
-      <c r="F152" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" t="s">
+      <c r="B154" t="s">
         <v>296</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C154" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
         <v>297</v>
       </c>
-      <c r="F153" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" t="s">
+      <c r="B155" t="s">
         <v>298</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C155" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
         <v>299</v>
       </c>
-      <c r="F154" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" t="s">
+      <c r="B156" t="s">
         <v>300</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C156" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
         <v>301</v>
       </c>
-      <c r="F155" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156" t="s">
+      <c r="B157" t="s">
         <v>302</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C157" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
         <v>303</v>
       </c>
-      <c r="F156" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157" t="s">
+      <c r="B158" t="s">
         <v>304</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C158" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
         <v>305</v>
       </c>
-      <c r="F157" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158" t="s">
+      <c r="B159" t="s">
         <v>306</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C159" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
         <v>307</v>
       </c>
-      <c r="F158" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159" t="s">
+      <c r="B160" t="s">
         <v>308</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C160" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
         <v>309</v>
       </c>
-      <c r="F159" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160" t="s">
+      <c r="C161" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
         <v>310</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B162" t="s">
         <v>311</v>
       </c>
-      <c r="F160" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161" t="s">
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
         <v>312</v>
       </c>
-      <c r="F161" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162" t="s">
+      <c r="B163" t="s">
         <v>313</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
         <v>314</v>
       </c>
-      <c r="F162" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163" t="s">
+      <c r="B164" t="s">
         <v>315</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C164" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
         <v>316</v>
       </c>
-      <c r="F163" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164" t="s">
+      <c r="B165" t="s">
         <v>317</v>
       </c>
-      <c r="B164" t="s">
+      <c r="C165" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
         <v>318</v>
       </c>
-      <c r="F164" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165" t="s">
+      <c r="B166" t="s">
         <v>319</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C166" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
         <v>320</v>
       </c>
-      <c r="F165" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166" t="s">
+      <c r="B167" t="s">
         <v>321</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C167" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
         <v>322</v>
       </c>
-      <c r="F166" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167" t="s">
+      <c r="B168" t="s">
         <v>323</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C168" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
         <v>324</v>
       </c>
-      <c r="F167" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168" t="s">
+      <c r="B169" t="s">
         <v>325</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C169" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
         <v>326</v>
       </c>
-      <c r="F168" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169" t="s">
+      <c r="B170" t="s">
         <v>327</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C170" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
         <v>328</v>
       </c>
-      <c r="F169" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170" t="s">
+      <c r="B171" t="s">
         <v>329</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C171" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
         <v>330</v>
       </c>
-      <c r="F170" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171" t="s">
+      <c r="B172" t="s">
         <v>331</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C172" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" t="s">
         <v>332</v>
       </c>
-      <c r="F171" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172" t="s">
+      <c r="C173" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" t="s">
         <v>333</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B174" t="s">
         <v>334</v>
       </c>
-      <c r="F172" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173" t="s">
+      <c r="C174" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
         <v>335</v>
       </c>
-      <c r="F173" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174" t="s">
+      <c r="B175" t="s">
         <v>336</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C175" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
         <v>337</v>
       </c>
-      <c r="F174" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175" t="s">
+      <c r="B176" t="s">
         <v>338</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C176" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" t="s">
         <v>339</v>
       </c>
-      <c r="F175" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176" t="s">
+      <c r="B177" t="s">
         <v>340</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C177" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" t="s">
         <v>341</v>
       </c>
-      <c r="F176" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177" t="s">
+      <c r="B178" t="s">
         <v>342</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C178" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" t="s">
         <v>343</v>
       </c>
-      <c r="F177" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178" t="s">
+      <c r="B179" t="s">
         <v>344</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C179" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" t="s">
         <v>345</v>
       </c>
-      <c r="F178" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179" t="s">
+      <c r="B180" t="s">
         <v>346</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C180" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" t="s">
         <v>347</v>
       </c>
-      <c r="F179" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180" t="s">
+      <c r="B181" t="s">
         <v>348</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C181" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" t="s">
         <v>349</v>
       </c>
-      <c r="F180" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181" t="s">
+      <c r="B182" t="s">
         <v>350</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C182" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" t="s">
         <v>351</v>
       </c>
-      <c r="F181" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182" t="s">
+      <c r="B183" t="s">
         <v>352</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C183" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" t="s">
         <v>353</v>
       </c>
-      <c r="F182" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183" t="s">
+      <c r="B184" t="s">
         <v>354</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C184" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" t="s">
         <v>355</v>
       </c>
-      <c r="F183" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184" t="s">
+      <c r="B185" t="s">
         <v>356</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C185" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" t="s">
         <v>357</v>
       </c>
-      <c r="F184" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185" t="s">
+      <c r="B186" t="s">
         <v>358</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C186" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" t="s">
         <v>359</v>
       </c>
-      <c r="F185" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186" t="s">
+      <c r="B187" t="s">
         <v>360</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C187" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" t="s">
         <v>361</v>
       </c>
-      <c r="F186" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187" t="s">
+      <c r="B188" t="s">
         <v>362</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C188" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" t="s">
         <v>363</v>
       </c>
-      <c r="F187" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188" t="s">
+      <c r="B189" t="s">
         <v>364</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C189" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" t="s">
         <v>365</v>
       </c>
-      <c r="F188" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189" t="s">
+      <c r="B190" t="s">
         <v>366</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" t="s">
         <v>367</v>
       </c>
-      <c r="F189" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190" t="s">
+      <c r="B191" t="s">
         <v>368</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C191" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
         <v>369</v>
       </c>
-      <c r="F190" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191" t="s">
+      <c r="B192" t="s">
         <v>370</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C192" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
         <v>371</v>
       </c>
-      <c r="F191" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192" t="s">
+      <c r="B193" t="s">
         <v>372</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C193" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
         <v>373</v>
       </c>
-      <c r="F192" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193" t="s">
+      <c r="B194" t="s">
         <v>374</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C194" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" t="s">
         <v>375</v>
       </c>
-      <c r="F193" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" t="s">
+      <c r="B195" t="s">
         <v>376</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C195" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" t="s">
         <v>377</v>
       </c>
-      <c r="F194" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195" t="s">
+      <c r="B196" t="s">
         <v>378</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C196" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" t="s">
         <v>379</v>
       </c>
-      <c r="F195" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196" t="s">
+      <c r="B197" t="s">
         <v>380</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C197" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" t="s">
         <v>381</v>
       </c>
-      <c r="F196" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197" t="s">
+      <c r="B198" t="s">
         <v>382</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
         <v>383</v>
       </c>
-      <c r="F197" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198" t="s">
+      <c r="B199" t="s">
         <v>384</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C199" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" t="s">
         <v>385</v>
       </c>
-      <c r="F198" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199" t="s">
+      <c r="B200" t="s">
         <v>386</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C200" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" t="s">
         <v>387</v>
       </c>
-      <c r="F199" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200" t="s">
+      <c r="B201" t="s">
         <v>388</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C201" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
         <v>389</v>
       </c>
-      <c r="F200" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201" t="s">
+      <c r="B202" t="s">
         <v>390</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C202" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" t="s">
         <v>391</v>
       </c>
-      <c r="F201" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202" t="s">
+      <c r="B203" t="s">
         <v>392</v>
       </c>
-      <c r="B202" t="s">
+      <c r="C203" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" t="s">
         <v>393</v>
       </c>
-      <c r="F202" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203" t="s">
+      <c r="B204" t="s">
         <v>394</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C204" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
         <v>395</v>
       </c>
-      <c r="F203" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204" t="s">
+      <c r="B205" t="s">
         <v>396</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C205" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" t="s">
         <v>397</v>
       </c>
-      <c r="F204" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205" t="s">
+      <c r="B206" t="s">
         <v>398</v>
       </c>
-      <c r="B205" t="s">
+      <c r="C206" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" t="s">
         <v>399</v>
       </c>
-      <c r="F205" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206" t="s">
+      <c r="B207" t="s">
         <v>400</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C207" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" t="s">
         <v>401</v>
       </c>
-      <c r="F206" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207" t="s">
+      <c r="B208" t="s">
         <v>402</v>
       </c>
-      <c r="B207" t="s">
+      <c r="C208" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" t="s">
         <v>403</v>
       </c>
-      <c r="F207" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208" t="s">
+      <c r="B209" t="s">
         <v>404</v>
       </c>
-      <c r="B208" t="s">
+      <c r="C209" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" t="s">
         <v>405</v>
       </c>
-      <c r="F208" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209" t="s">
+      <c r="B210" t="s">
         <v>406</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C210" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" t="s">
         <v>407</v>
       </c>
-      <c r="F209" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210" t="s">
+      <c r="B211" t="s">
         <v>408</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C211" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" t="s">
         <v>409</v>
       </c>
-      <c r="F210" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211" t="s">
+      <c r="B212" t="s">
         <v>410</v>
       </c>
-      <c r="B211" t="s">
+      <c r="C212" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" t="s">
         <v>411</v>
       </c>
-      <c r="F211" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212" t="s">
+      <c r="B213" t="s">
         <v>412</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C213" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" t="s">
         <v>413</v>
       </c>
-      <c r="F212" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213" t="s">
+      <c r="B214" t="s">
         <v>414</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C214" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" t="s">
         <v>415</v>
       </c>
-      <c r="F213" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214" t="s">
+      <c r="B215" t="s">
         <v>416</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C215" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216" t="s">
         <v>417</v>
       </c>
-      <c r="F214" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215" t="s">
+      <c r="B216" t="s">
         <v>418</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C216" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" t="s">
         <v>419</v>
       </c>
-      <c r="F215" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216" t="s">
+      <c r="B217" t="s">
         <v>420</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C217" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" t="s">
         <v>421</v>
       </c>
-      <c r="F216" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217" t="s">
+      <c r="B218" t="s">
         <v>422</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219" t="s">
         <v>423</v>
       </c>
-      <c r="F217" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218" t="s">
+      <c r="B219" t="s">
         <v>424</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C219" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220" t="s">
         <v>425</v>
       </c>
-      <c r="F218" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219" t="s">
+      <c r="B220" t="s">
         <v>426</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C220" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" t="s">
         <v>427</v>
       </c>
-      <c r="F219" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
-      <c r="A220" t="s">
+      <c r="B221" t="s">
         <v>428</v>
       </c>
-      <c r="B220" t="s">
+      <c r="C221" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" t="s">
         <v>429</v>
       </c>
-      <c r="F220" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221" t="s">
+      <c r="B222" t="s">
         <v>430</v>
       </c>
-      <c r="B221" t="s">
+      <c r="C222" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" t="s">
         <v>431</v>
       </c>
-      <c r="F221" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222" t="s">
+      <c r="B223" t="s">
         <v>432</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C223" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" t="s">
         <v>433</v>
       </c>
-      <c r="F222" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
-      <c r="A223" t="s">
+      <c r="B224" t="s">
         <v>434</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C224" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" t="s">
         <v>435</v>
       </c>
-      <c r="F223" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
-      <c r="A224" t="s">
+      <c r="B225" t="s">
         <v>436</v>
       </c>
-      <c r="B224" t="s">
+      <c r="C225" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" t="s">
         <v>437</v>
       </c>
-      <c r="F224" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
-      <c r="A225" t="s">
+      <c r="B226" t="s">
         <v>438</v>
       </c>
-      <c r="B225" t="s">
+      <c r="C226" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" t="s">
         <v>439</v>
       </c>
-      <c r="F225" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
-      <c r="A226" t="s">
+      <c r="B227" t="s">
         <v>440</v>
       </c>
-      <c r="B226" t="s">
+      <c r="C227" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" t="s">
         <v>441</v>
       </c>
-      <c r="F226" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6">
-      <c r="A227" t="s">
+      <c r="B228" t="s">
         <v>442</v>
       </c>
-      <c r="B227" t="s">
+      <c r="C228" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" t="s">
         <v>443</v>
       </c>
-      <c r="F227" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6">
-      <c r="A228" t="s">
+      <c r="B229" t="s">
         <v>444</v>
       </c>
-      <c r="B228" t="s">
+      <c r="C229" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" t="s">
         <v>445</v>
       </c>
-      <c r="F228" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6">
-      <c r="A229" t="s">
+      <c r="B230" t="s">
         <v>446</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" t="s">
         <v>447</v>
       </c>
-      <c r="F229" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6">
-      <c r="A230" t="s">
+      <c r="B231" t="s">
         <v>448</v>
       </c>
-      <c r="B230" t="s">
+      <c r="C231" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" t="s">
         <v>449</v>
       </c>
-      <c r="F230" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6">
-      <c r="A231" t="s">
+      <c r="B232" t="s">
         <v>450</v>
       </c>
-      <c r="B231" t="s">
+      <c r="C232" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" t="s">
         <v>451</v>
       </c>
-      <c r="F231" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
-      <c r="A232" t="s">
+      <c r="B233" t="s">
         <v>452</v>
       </c>
-      <c r="B232" t="s">
+      <c r="C233" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" t="s">
         <v>453</v>
       </c>
-      <c r="F232" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
-      <c r="A233" t="s">
+      <c r="B234" t="s">
         <v>454</v>
       </c>
-      <c r="B233" t="s">
+      <c r="C234" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" t="s">
         <v>455</v>
       </c>
-      <c r="F233" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
-      <c r="A234" t="s">
+      <c r="B235" t="s">
         <v>456</v>
       </c>
-      <c r="B234" t="s">
+      <c r="C235" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" t="s">
         <v>457</v>
       </c>
-      <c r="F234" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
-      <c r="A235" t="s">
+      <c r="B236" t="s">
         <v>458</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C236" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" t="s">
         <v>459</v>
       </c>
-      <c r="F235" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
-      <c r="A236" t="s">
+      <c r="B237" t="s">
         <v>460</v>
       </c>
-      <c r="B236" t="s">
+      <c r="C237" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" t="s">
         <v>461</v>
       </c>
-      <c r="F236" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
-      <c r="A237" t="s">
+      <c r="B238" t="s">
         <v>462</v>
       </c>
-      <c r="B237" t="s">
+      <c r="C238" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" t="s">
         <v>463</v>
       </c>
-      <c r="F237" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6">
-      <c r="A238" t="s">
+      <c r="B239" t="s">
         <v>464</v>
       </c>
-      <c r="B238" t="s">
+      <c r="C239" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" t="s">
         <v>465</v>
       </c>
-      <c r="F238" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6">
-      <c r="A239" t="s">
+      <c r="C240" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" t="s">
         <v>466</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B241" t="s">
         <v>467</v>
       </c>
-      <c r="F239" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6">
-      <c r="A240" t="s">
+      <c r="C241" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" t="s">
         <v>468</v>
       </c>
-      <c r="F240" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
-      <c r="A241" t="s">
+      <c r="B242" t="s">
         <v>469</v>
       </c>
-      <c r="B241" t="s">
+      <c r="C242" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" t="s">
         <v>470</v>
       </c>
-      <c r="F241" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
-      <c r="A242" t="s">
+      <c r="B243" t="s">
         <v>471</v>
       </c>
-      <c r="B242" t="s">
+      <c r="C243" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" t="s">
         <v>472</v>
       </c>
-      <c r="F242" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
-      <c r="A243" t="s">
+      <c r="B244" t="s">
         <v>473</v>
       </c>
-      <c r="B243" t="s">
+      <c r="C244" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" t="s">
         <v>474</v>
       </c>
-      <c r="F243" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6">
-      <c r="A244" t="s">
+      <c r="B245" t="s">
         <v>475</v>
       </c>
-      <c r="B244" t="s">
+      <c r="C245" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" t="s">
         <v>476</v>
       </c>
-      <c r="F244" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
-      <c r="A245" t="s">
+      <c r="B246" t="s">
         <v>477</v>
       </c>
-      <c r="B245" t="s">
+      <c r="C246" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" t="s">
         <v>478</v>
       </c>
-      <c r="F245" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246" t="s">
+      <c r="B247" t="s">
         <v>479</v>
       </c>
-      <c r="B246" t="s">
+      <c r="C247" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" t="s">
         <v>480</v>
       </c>
-      <c r="F246" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
-      <c r="A247" t="s">
+      <c r="B248" t="s">
         <v>481</v>
       </c>
-      <c r="B247" t="s">
+      <c r="C248" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" t="s">
         <v>482</v>
       </c>
-      <c r="F247" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
-      <c r="A248" t="s">
+      <c r="B249" t="s">
         <v>483</v>
       </c>
-      <c r="B248" t="s">
+      <c r="C249" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" t="s">
         <v>484</v>
       </c>
-      <c r="F248" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
-      <c r="A249" t="s">
+      <c r="B250" t="s">
         <v>485</v>
       </c>
-      <c r="B249" t="s">
+      <c r="C250" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" t="s">
         <v>486</v>
       </c>
-      <c r="F249" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250" t="s">
+      <c r="B251" t="s">
         <v>487</v>
       </c>
-      <c r="B250" t="s">
+      <c r="C251" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" t="s">
         <v>488</v>
       </c>
-      <c r="F250" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
-      <c r="A251" t="s">
+      <c r="B252" t="s">
         <v>489</v>
       </c>
-      <c r="B251" t="s">
+      <c r="C252" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" t="s">
         <v>490</v>
       </c>
-      <c r="F251" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
-      <c r="A252" t="s">
+      <c r="B253" t="s">
         <v>491</v>
       </c>
-      <c r="B252" t="s">
+      <c r="C253" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" t="s">
         <v>492</v>
       </c>
-      <c r="F252" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
-      <c r="A253" t="s">
+      <c r="B254" t="s">
         <v>493</v>
       </c>
-      <c r="B253" t="s">
+      <c r="C254" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" t="s">
         <v>494</v>
       </c>
-      <c r="F253" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6">
-      <c r="A254" t="s">
+      <c r="B255" t="s">
         <v>495</v>
       </c>
-      <c r="B254" t="s">
+      <c r="C255" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" t="s">
         <v>496</v>
       </c>
-      <c r="F254" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
-      <c r="A255" t="s">
+      <c r="C256" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" t="s">
         <v>497</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B257" t="s">
         <v>498</v>
       </c>
-      <c r="F255" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
-      <c r="A256" t="s">
+      <c r="C257" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
         <v>499</v>
       </c>
-      <c r="F256" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
-      <c r="A257" t="s">
+      <c r="B258" t="s">
         <v>500</v>
       </c>
-      <c r="B257" t="s">
+      <c r="C258" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" t="s">
         <v>501</v>
       </c>
-      <c r="F257" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
-      <c r="A258" t="s">
+      <c r="B259" t="s">
         <v>502</v>
       </c>
-      <c r="B258" t="s">
+      <c r="C259" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" t="s">
         <v>503</v>
       </c>
-      <c r="F258" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
-      <c r="A259" t="s">
+      <c r="C260" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261" t="s">
         <v>504</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B261" t="s">
         <v>505</v>
       </c>
-      <c r="F259" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
-      <c r="A260" t="s">
+      <c r="C261" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262" t="s">
         <v>506</v>
       </c>
-      <c r="F260" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
-      <c r="A261" t="s">
+      <c r="B262" t="s">
         <v>507</v>
       </c>
-      <c r="B261" t="s">
+      <c r="C262" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" t="s">
         <v>508</v>
       </c>
-      <c r="F261" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
-      <c r="A262" t="s">
+      <c r="B263" t="s">
         <v>509</v>
       </c>
-      <c r="B262" t="s">
+      <c r="C263" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" t="s">
         <v>510</v>
       </c>
-      <c r="F262" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
-      <c r="A263" t="s">
+      <c r="B264" t="s">
         <v>511</v>
       </c>
-      <c r="B263" t="s">
+      <c r="C264" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" t="s">
         <v>512</v>
       </c>
-      <c r="F263" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="A264" t="s">
+      <c r="C265" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" t="s">
         <v>513</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B266" t="s">
         <v>514</v>
       </c>
-      <c r="F264" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
-      <c r="A265" t="s">
+      <c r="C266" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" t="s">
         <v>515</v>
       </c>
-      <c r="F265" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
-      <c r="A266" t="s">
+      <c r="B267" t="s">
         <v>516</v>
       </c>
-      <c r="B266" t="s">
+      <c r="C267" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268" t="s">
         <v>517</v>
       </c>
-      <c r="F266" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="A267" t="s">
+      <c r="B268" t="s">
         <v>518</v>
       </c>
-      <c r="B267" t="s">
+      <c r="C268" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" t="s">
         <v>519</v>
       </c>
-      <c r="F267" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
-      <c r="A268" t="s">
+      <c r="B269" t="s">
         <v>520</v>
       </c>
-      <c r="B268" t="s">
+      <c r="C269" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" t="s">
         <v>521</v>
       </c>
-      <c r="F268" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
-      <c r="A269" t="s">
+      <c r="B270" t="s">
         <v>522</v>
       </c>
-      <c r="B269" t="s">
+      <c r="C270" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" t="s">
         <v>523</v>
       </c>
-      <c r="F269" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
-      <c r="A270" t="s">
+      <c r="B271" t="s">
         <v>524</v>
       </c>
-      <c r="B270" t="s">
+      <c r="C271" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" t="s">
         <v>525</v>
       </c>
-      <c r="F270" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
-      <c r="A271" t="s">
+      <c r="B272" t="s">
         <v>526</v>
       </c>
-      <c r="B271" t="s">
+      <c r="C272" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273" t="s">
         <v>527</v>
       </c>
-      <c r="F271" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
-      <c r="A272" t="s">
+      <c r="B273" t="s">
         <v>528</v>
       </c>
-      <c r="B272" t="s">
+      <c r="C273" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274" t="s">
         <v>529</v>
       </c>
-      <c r="F272" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
-      <c r="A273" t="s">
+      <c r="B274" t="s">
         <v>530</v>
       </c>
-      <c r="B273" t="s">
+      <c r="C274" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" t="s">
         <v>531</v>
       </c>
-      <c r="F273" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
-      <c r="A274" t="s">
+      <c r="B275" t="s">
         <v>532</v>
       </c>
-      <c r="B274" t="s">
+      <c r="C275" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" t="s">
         <v>533</v>
       </c>
-      <c r="F274" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6">
-      <c r="A275" t="s">
+      <c r="B276" t="s">
         <v>534</v>
       </c>
-      <c r="B275" t="s">
+      <c r="C276" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" t="s">
         <v>535</v>
       </c>
-      <c r="F275" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
-      <c r="A276" t="s">
+      <c r="B277" t="s">
         <v>536</v>
       </c>
-      <c r="B276" t="s">
+      <c r="C277" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" t="s">
         <v>537</v>
       </c>
-      <c r="F276" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
-      <c r="A277" t="s">
+      <c r="B278" t="s">
         <v>538</v>
       </c>
-      <c r="B277" t="s">
+      <c r="C278" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" t="s">
         <v>539</v>
       </c>
-      <c r="F277" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
-      <c r="A278" t="s">
+      <c r="B279" t="s">
         <v>540</v>
       </c>
-      <c r="B278" t="s">
+      <c r="C279" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" t="s">
         <v>541</v>
       </c>
-      <c r="F278" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
-      <c r="A279" t="s">
+      <c r="B280" t="s">
         <v>542</v>
       </c>
-      <c r="B279" t="s">
+      <c r="C280" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
         <v>543</v>
       </c>
-      <c r="F279" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
-      <c r="A280" t="s">
+      <c r="B281" t="s">
         <v>544</v>
       </c>
-      <c r="B280" t="s">
+      <c r="C281" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" t="s">
         <v>545</v>
       </c>
-      <c r="F280" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
-      <c r="A281" t="s">
+      <c r="B282" t="s">
         <v>546</v>
       </c>
-      <c r="B281" t="s">
+      <c r="C282" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283" t="s">
         <v>547</v>
       </c>
-      <c r="F281" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
-      <c r="A282" t="s">
+      <c r="B283" t="s">
         <v>548</v>
       </c>
-      <c r="B282" t="s">
+      <c r="C283" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" t="s">
         <v>549</v>
       </c>
-      <c r="F282" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
-      <c r="A283" t="s">
+      <c r="C284" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" t="s">
         <v>550</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B285" t="s">
         <v>551</v>
       </c>
-      <c r="F283" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
-      <c r="A284" t="s">
+      <c r="C285" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" t="s">
         <v>552</v>
       </c>
-      <c r="F284" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
-      <c r="A285" t="s">
+      <c r="B286" t="s">
         <v>553</v>
       </c>
-      <c r="B285" t="s">
+      <c r="C286" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" t="s">
         <v>554</v>
       </c>
-      <c r="F285" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
-      <c r="A286" t="s">
+      <c r="B287" t="s">
         <v>555</v>
       </c>
-      <c r="B286" t="s">
+      <c r="C287" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" t="s">
         <v>556</v>
       </c>
-      <c r="F286" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
-      <c r="A287" t="s">
+      <c r="B288" t="s">
         <v>557</v>
       </c>
-      <c r="B287" t="s">
+      <c r="C288" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" t="s">
         <v>558</v>
       </c>
-      <c r="F287" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
-      <c r="A288" t="s">
+      <c r="B289" t="s">
         <v>559</v>
       </c>
-      <c r="B288" t="s">
+      <c r="C289" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" t="s">
         <v>560</v>
       </c>
-      <c r="F288" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6">
-      <c r="A289" t="s">
+      <c r="B290" t="s">
         <v>561</v>
       </c>
-      <c r="B289" t="s">
+      <c r="C290" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" t="s">
         <v>562</v>
       </c>
-      <c r="F289" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
-      <c r="A290" t="s">
+      <c r="B291" t="s">
         <v>563</v>
       </c>
-      <c r="B290" t="s">
+      <c r="C291" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292" t="s">
         <v>564</v>
       </c>
-      <c r="F290" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
-      <c r="A291" t="s">
+      <c r="B292" t="s">
         <v>565</v>
       </c>
-      <c r="B291" t="s">
+      <c r="C292" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293" t="s">
         <v>566</v>
       </c>
-      <c r="F291" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
-      <c r="A292" t="s">
+      <c r="B293" t="s">
         <v>567</v>
       </c>
-      <c r="B292" t="s">
+      <c r="C293" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" t="s">
         <v>568</v>
       </c>
-      <c r="F292" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
-      <c r="A293" t="s">
+      <c r="B294" t="s">
         <v>569</v>
       </c>
-      <c r="B293" t="s">
+      <c r="C294" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295" t="s">
         <v>570</v>
       </c>
-      <c r="F293" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
-      <c r="A294" t="s">
+      <c r="B295" t="s">
         <v>571</v>
       </c>
-      <c r="B294" t="s">
+      <c r="C295" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" t="s">
         <v>572</v>
       </c>
-      <c r="F294" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
-      <c r="A295" t="s">
+      <c r="B296" t="s">
         <v>573</v>
       </c>
-      <c r="B295" t="s">
+      <c r="C296" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297" t="s">
         <v>574</v>
       </c>
-      <c r="F295" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
-      <c r="A296" t="s">
+      <c r="B297" t="s">
         <v>575</v>
       </c>
-      <c r="B296" t="s">
+      <c r="C297" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" t="s">
         <v>576</v>
       </c>
-      <c r="F296" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6">
-      <c r="A297" t="s">
+      <c r="B298" t="s">
         <v>577</v>
       </c>
-      <c r="B297" t="s">
+      <c r="C298" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" t="s">
         <v>578</v>
       </c>
-      <c r="F297" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6">
-      <c r="A298" t="s">
+      <c r="B299" t="s">
         <v>579</v>
       </c>
-      <c r="B298" t="s">
+      <c r="C299" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" t="s">
         <v>580</v>
       </c>
-      <c r="F298" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6">
-      <c r="A299" t="s">
+      <c r="B300" t="s">
         <v>581</v>
       </c>
-      <c r="B299" t="s">
+      <c r="C300" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" t="s">
         <v>582</v>
       </c>
-      <c r="F299" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6">
-      <c r="A300" t="s">
+      <c r="B301" t="s">
         <v>583</v>
       </c>
-      <c r="B300" t="s">
+      <c r="C301" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" t="s">
         <v>584</v>
       </c>
-      <c r="F300" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6">
-      <c r="A301" t="s">
+      <c r="B302" t="s">
         <v>585</v>
       </c>
-      <c r="B301" t="s">
+      <c r="C302" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" t="s">
         <v>586</v>
       </c>
-      <c r="F301" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6">
-      <c r="A302" t="s">
+      <c r="B303" t="s">
         <v>587</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C303" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" t="s">
         <v>588</v>
       </c>
-      <c r="F302" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6">
-      <c r="A303" t="s">
+      <c r="B304" t="s">
         <v>589</v>
       </c>
-      <c r="B303" t="s">
+      <c r="C304" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
         <v>590</v>
       </c>
-      <c r="F303" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6">
-      <c r="A304" t="s">
+      <c r="B305" t="s">
         <v>591</v>
       </c>
-      <c r="B304" t="s">
+      <c r="C305" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" t="s">
         <v>592</v>
       </c>
-      <c r="F304" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6">
-      <c r="A305" t="s">
+      <c r="B306" t="s">
         <v>593</v>
       </c>
-      <c r="B305" t="s">
+      <c r="C306" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" t="s">
         <v>594</v>
       </c>
-      <c r="F305" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6">
-      <c r="A306" t="s">
+      <c r="B307" t="s">
         <v>595</v>
       </c>
-      <c r="B306" t="s">
+      <c r="C307" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" t="s">
         <v>596</v>
       </c>
-      <c r="F306" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6">
-      <c r="A307" t="s">
+      <c r="B308" t="s">
         <v>597</v>
       </c>
-      <c r="B307" t="s">
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" t="s">
         <v>598</v>
       </c>
-      <c r="F307" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6">
-      <c r="A308" t="s">
+      <c r="B309" t="s">
         <v>599</v>
       </c>
-      <c r="B308" t="s">
+      <c r="C309" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310" t="s">
         <v>600</v>
       </c>
-      <c r="F308" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6">
-      <c r="A309" t="s">
+      <c r="B310" t="s">
         <v>601</v>
       </c>
-      <c r="B309" t="s">
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" t="s">
         <v>602</v>
       </c>
-      <c r="F309" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6">
-      <c r="A310" t="s">
+      <c r="B311" t="s">
         <v>603</v>
       </c>
-      <c r="B310" t="s">
+      <c r="C311" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" t="s">
         <v>604</v>
       </c>
-      <c r="F310" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6">
-      <c r="A311" t="s">
+      <c r="B312" t="s">
         <v>605</v>
       </c>
-      <c r="B311" t="s">
+      <c r="C312" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313" t="s">
         <v>606</v>
       </c>
-      <c r="F311" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6">
-      <c r="A312" t="s">
+      <c r="B313" t="s">
         <v>607</v>
       </c>
-      <c r="B312" t="s">
+      <c r="C313" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" t="s">
         <v>608</v>
       </c>
-      <c r="F312" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6">
-      <c r="A313" t="s">
+      <c r="B314" t="s">
         <v>609</v>
       </c>
-      <c r="B313" t="s">
+      <c r="C314" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" t="s">
         <v>610</v>
       </c>
-      <c r="F313" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6">
-      <c r="A314" t="s">
+      <c r="B315" t="s">
         <v>611</v>
       </c>
-      <c r="B314" t="s">
+      <c r="C315" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316" t="s">
         <v>612</v>
       </c>
-      <c r="F314" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6">
-      <c r="A315" t="s">
+      <c r="B316" t="s">
         <v>613</v>
       </c>
-      <c r="B315" t="s">
+      <c r="C316" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" t="s">
         <v>614</v>
       </c>
-      <c r="F315" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6">
-      <c r="A316" t="s">
+      <c r="B317" t="s">
         <v>615</v>
       </c>
-      <c r="B316" t="s">
+      <c r="C317" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" t="s">
         <v>616</v>
       </c>
-      <c r="F316" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6">
-      <c r="A317" t="s">
+      <c r="B318" t="s">
         <v>617</v>
       </c>
-      <c r="B317" t="s">
+      <c r="C318" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" t="s">
         <v>618</v>
       </c>
-      <c r="F317" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6">
-      <c r="A318" t="s">
+      <c r="B319" t="s">
         <v>619</v>
       </c>
-      <c r="B318" t="s">
+      <c r="C319" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" t="s">
         <v>620</v>
       </c>
-      <c r="F318" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6">
-      <c r="A319" t="s">
+      <c r="B320" t="s">
         <v>621</v>
       </c>
-      <c r="B319" t="s">
+      <c r="C320" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" t="s">
         <v>622</v>
       </c>
-      <c r="F319" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6">
-      <c r="A320" t="s">
+      <c r="B321" t="s">
         <v>623</v>
       </c>
-      <c r="B320" t="s">
+      <c r="C321" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" t="s">
         <v>624</v>
       </c>
-      <c r="F320" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6">
-      <c r="A321" t="s">
+      <c r="B322" t="s">
         <v>625</v>
       </c>
-      <c r="B321" t="s">
+      <c r="C322" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" t="s">
         <v>626</v>
       </c>
-      <c r="F321" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6">
-      <c r="A322" t="s">
+      <c r="C323" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" t="s">
         <v>627</v>
       </c>
-      <c r="B322" t="s">
+      <c r="B324" t="s">
         <v>628</v>
       </c>
-      <c r="F322" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6">
-      <c r="A323" t="s">
+      <c r="C324" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
         <v>629</v>
       </c>
-      <c r="F323" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6">
-      <c r="A324" t="s">
+      <c r="B325" t="s">
         <v>630</v>
       </c>
-      <c r="B324" t="s">
+      <c r="C325" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" t="s">
         <v>631</v>
       </c>
-      <c r="F324" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="325" spans="1:6">
-      <c r="A325" t="s">
+      <c r="B326" t="s">
         <v>632</v>
       </c>
-      <c r="B325" t="s">
+      <c r="C326" t="s">
         <v>633</v>
       </c>
-      <c r="F325" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6">
-      <c r="A326" t="s">
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" t="s">
         <v>634</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B327" t="s">
         <v>635</v>
       </c>
-      <c r="F326" t="s">
+      <c r="C327" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="327" spans="1:6">
-      <c r="A327" t="s">
+      <c r="B328" t="s">
         <v>637</v>
       </c>
-      <c r="B327" t="s">
+      <c r="C328" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" t="s">
         <v>638</v>
       </c>
-      <c r="F327" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6">
-      <c r="A328" t="s">
+      <c r="B329" t="s">
         <v>639</v>
       </c>
-      <c r="B328" t="s">
+      <c r="C329" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" t="s">
         <v>640</v>
       </c>
-      <c r="F328" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6">
-      <c r="A329" t="s">
+      <c r="B330" t="s">
         <v>641</v>
       </c>
-      <c r="B329" t="s">
+      <c r="C330" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" t="s">
         <v>642</v>
       </c>
-      <c r="F329" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6">
-      <c r="A330" t="s">
+      <c r="B331" t="s">
         <v>643</v>
       </c>
-      <c r="B330" t="s">
+      <c r="C331" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" t="s">
         <v>644</v>
       </c>
-      <c r="F330" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6">
-      <c r="A331" t="s">
+      <c r="B332" t="s">
         <v>645</v>
       </c>
-      <c r="B331" t="s">
+      <c r="C332" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" t="s">
         <v>646</v>
       </c>
-      <c r="F331" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6">
-      <c r="A332" t="s">
+      <c r="B333" t="s">
         <v>647</v>
       </c>
-      <c r="B332" t="s">
+      <c r="C333" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" t="s">
         <v>648</v>
       </c>
-      <c r="F332" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6">
-      <c r="A333" t="s">
+      <c r="B334" t="s">
         <v>649</v>
       </c>
-      <c r="B333" t="s">
+      <c r="C334" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" t="s">
         <v>650</v>
       </c>
-      <c r="F333" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6">
-      <c r="A334" t="s">
+      <c r="B335" t="s">
         <v>651</v>
       </c>
-      <c r="B334" t="s">
+      <c r="C335" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" t="s">
         <v>652</v>
       </c>
-      <c r="F334" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6">
-      <c r="A335" t="s">
+      <c r="B336" t="s">
         <v>653</v>
       </c>
-      <c r="B335" t="s">
+      <c r="C336" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" t="s">
         <v>654</v>
       </c>
-      <c r="F335" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6">
-      <c r="A336" t="s">
+      <c r="B337" t="s">
         <v>655</v>
       </c>
-      <c r="B336" t="s">
+      <c r="C337" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" t="s">
         <v>656</v>
       </c>
-      <c r="F336" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6">
-      <c r="A337" t="s">
+      <c r="B338" t="s">
         <v>657</v>
       </c>
-      <c r="B337" t="s">
+      <c r="C338" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" t="s">
         <v>658</v>
       </c>
-      <c r="F337" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6">
-      <c r="A338" t="s">
+      <c r="B339" t="s">
         <v>659</v>
       </c>
-      <c r="B338" t="s">
+      <c r="C339" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" t="s">
         <v>660</v>
       </c>
-      <c r="F338" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6">
-      <c r="A339" t="s">
+      <c r="B340" t="s">
         <v>661</v>
       </c>
-      <c r="B339" t="s">
+      <c r="C340" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" t="s">
         <v>662</v>
       </c>
-      <c r="F339" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6">
-      <c r="A340" t="s">
+      <c r="B341" t="s">
         <v>663</v>
       </c>
-      <c r="B340" t="s">
+      <c r="C341" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" t="s">
         <v>664</v>
       </c>
-      <c r="F340" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6">
-      <c r="A341" t="s">
+      <c r="B342" t="s">
         <v>665</v>
       </c>
-      <c r="B341" t="s">
+      <c r="C342" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" t="s">
         <v>666</v>
       </c>
-      <c r="F341" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6">
-      <c r="A342" t="s">
+      <c r="B343" t="s">
         <v>667</v>
       </c>
-      <c r="B342" t="s">
+      <c r="C343" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344" t="s">
         <v>668</v>
       </c>
-      <c r="F342" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6">
-      <c r="A343" t="s">
+      <c r="B344" t="s">
         <v>669</v>
       </c>
-      <c r="B343" t="s">
+      <c r="C344" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345" t="s">
         <v>670</v>
       </c>
-      <c r="F343" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="344" spans="1:6">
-      <c r="A344" t="s">
+      <c r="B345" t="s">
         <v>671</v>
       </c>
-      <c r="B344" t="s">
+      <c r="C345" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346" t="s">
         <v>672</v>
       </c>
-      <c r="F344" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6">
-      <c r="A345" t="s">
+      <c r="B346" t="s">
         <v>673</v>
       </c>
-      <c r="B345" t="s">
+      <c r="C346" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347" t="s">
         <v>674</v>
       </c>
-      <c r="F345" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6">
-      <c r="A346" t="s">
+      <c r="B347" t="s">
         <v>675</v>
       </c>
-      <c r="B346" t="s">
+      <c r="C347" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348" t="s">
         <v>676</v>
       </c>
-      <c r="F346" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6">
-      <c r="A347" t="s">
+      <c r="B348" t="s">
         <v>677</v>
       </c>
-      <c r="B347" t="s">
+      <c r="C348" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349" t="s">
         <v>678</v>
       </c>
-      <c r="F347" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6">
-      <c r="A348" t="s">
+      <c r="B349" t="s">
         <v>679</v>
       </c>
-      <c r="B348" t="s">
+      <c r="C349" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" t="s">
         <v>680</v>
       </c>
-      <c r="F348" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6">
-      <c r="A349" t="s">
+      <c r="B350" t="s">
         <v>681</v>
       </c>
-      <c r="B349" t="s">
+      <c r="C350" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" t="s">
         <v>682</v>
       </c>
-      <c r="F349" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6">
-      <c r="A350" t="s">
+      <c r="B351" t="s">
         <v>683</v>
       </c>
-      <c r="B350" t="s">
+      <c r="C351" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" t="s">
         <v>684</v>
       </c>
-      <c r="F350" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6">
-      <c r="A351" t="s">
+      <c r="B352" t="s">
         <v>685</v>
       </c>
-      <c r="B351" t="s">
+      <c r="C352" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" t="s">
         <v>686</v>
       </c>
-      <c r="F351" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6">
-      <c r="A352" t="s">
+      <c r="B353" t="s">
         <v>687</v>
       </c>
-      <c r="B352" t="s">
+      <c r="C353" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" t="s">
         <v>688</v>
       </c>
-      <c r="F352" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6">
-      <c r="A353" t="s">
+      <c r="B354" t="s">
         <v>689</v>
       </c>
-      <c r="B353" t="s">
+      <c r="C354" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" t="s">
         <v>690</v>
       </c>
-      <c r="F353" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6">
-      <c r="A354" t="s">
+      <c r="B355" t="s">
         <v>691</v>
       </c>
-      <c r="B354" t="s">
+      <c r="C355" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" t="s">
         <v>692</v>
       </c>
-      <c r="F354" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6">
-      <c r="A355" t="s">
+      <c r="B356" t="s">
+        <v>632</v>
+      </c>
+      <c r="C356" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" t="s">
         <v>693</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B357" t="s">
         <v>694</v>
       </c>
-      <c r="F355" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6">
-      <c r="A356" t="s">
+      <c r="C357" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358" t="s">
         <v>695</v>
       </c>
-      <c r="B356" t="s">
-        <v>635</v>
-      </c>
-      <c r="F356" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6">
-      <c r="A357" t="s">
+      <c r="B358" t="s">
         <v>696</v>
       </c>
-      <c r="B357" t="s">
+      <c r="C358" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359" t="s">
         <v>697</v>
       </c>
-      <c r="F357" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="358" spans="1:6">
-      <c r="A358" t="s">
+      <c r="C359" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360" t="s">
         <v>698</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B360" t="s">
         <v>699</v>
       </c>
-      <c r="F358" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="359" spans="1:6">
-      <c r="A359" t="s">
+      <c r="C360" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" t="s">
         <v>700</v>
       </c>
-      <c r="F359" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="360" spans="1:6">
-      <c r="A360" t="s">
+      <c r="C361" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" t="s">
         <v>701</v>
       </c>
-      <c r="B360" t="s">
+      <c r="C362" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363" t="s">
         <v>702</v>
       </c>
-      <c r="F360" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6">
-      <c r="A361" t="s">
+      <c r="C363" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" t="s">
         <v>703</v>
       </c>
-      <c r="F361" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="362" spans="1:6">
-      <c r="A362" t="s">
+      <c r="C364" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365" t="s">
         <v>704</v>
       </c>
-      <c r="F362" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6">
-      <c r="A363" t="s">
+      <c r="C365" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366" t="s">
         <v>705</v>
       </c>
-      <c r="F363" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="364" spans="1:6">
-      <c r="A364" t="s">
+      <c r="C366" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367" t="s">
         <v>706</v>
       </c>
-      <c r="F364" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="365" spans="1:6">
-      <c r="A365" t="s">
+      <c r="C367" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368" t="s">
         <v>707</v>
       </c>
-      <c r="F365" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="366" spans="1:6">
-      <c r="A366" t="s">
+      <c r="C368" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369" t="s">
         <v>708</v>
       </c>
-      <c r="F366" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="367" spans="1:6">
-      <c r="A367" t="s">
+      <c r="B369" t="s">
         <v>709</v>
       </c>
-      <c r="F367" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="368" spans="1:6">
-      <c r="A368" t="s">
+      <c r="C369" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370" t="s">
         <v>710</v>
       </c>
-      <c r="F368" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="369" spans="1:6">
-      <c r="A369" t="s">
+      <c r="C370" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" t="s">
         <v>711</v>
       </c>
-      <c r="B369" t="s">
+      <c r="C371" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372" t="s">
         <v>712</v>
       </c>
-      <c r="F369" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="370" spans="1:6">
-      <c r="A370" t="s">
+      <c r="C372" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373" t="s">
         <v>713</v>
       </c>
-      <c r="F370" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="371" spans="1:6">
-      <c r="A371" t="s">
+      <c r="C373" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374" t="s">
         <v>714</v>
       </c>
-      <c r="F371" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="372" spans="1:6">
-      <c r="A372" t="s">
+      <c r="C374" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375" t="s">
         <v>715</v>
       </c>
-      <c r="F372" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="373" spans="1:6">
-      <c r="A373" t="s">
+      <c r="C375" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" t="s">
         <v>716</v>
       </c>
-      <c r="F373" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6">
-      <c r="A374" t="s">
+      <c r="C376" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" t="s">
         <v>717</v>
       </c>
-      <c r="F374" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="375" spans="1:6">
-      <c r="A375" t="s">
+      <c r="C377" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" t="s">
         <v>718</v>
       </c>
-      <c r="F375" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="376" spans="1:6">
-      <c r="A376" t="s">
+      <c r="C378" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" t="s">
         <v>719</v>
       </c>
-      <c r="F376" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="377" spans="1:6">
-      <c r="A377" t="s">
+      <c r="C379" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" t="s">
         <v>720</v>
       </c>
-      <c r="F377" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="378" spans="1:6">
-      <c r="A378" t="s">
+      <c r="B380" t="s">
         <v>721</v>
       </c>
-      <c r="F378" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="379" spans="1:6">
-      <c r="A379" t="s">
+      <c r="C380" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" t="s">
         <v>722</v>
       </c>
-      <c r="F379" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="380" spans="1:6">
-      <c r="A380" t="s">
+      <c r="C381" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" t="s">
         <v>723</v>
       </c>
-      <c r="B380" t="s">
+      <c r="C382" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" t="s">
         <v>724</v>
       </c>
-      <c r="F380" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6">
-      <c r="A381" t="s">
+      <c r="C383" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384" t="s">
         <v>725</v>
       </c>
-      <c r="F381" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6">
-      <c r="A382" t="s">
+      <c r="C384" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385" t="s">
         <v>726</v>
       </c>
-      <c r="F382" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6">
-      <c r="A383" t="s">
+      <c r="C385" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386" t="s">
         <v>727</v>
       </c>
-      <c r="F383" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6">
-      <c r="A384" t="s">
+      <c r="C386" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387" t="s">
         <v>728</v>
       </c>
-      <c r="F384" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6">
-      <c r="A385" t="s">
+      <c r="C387" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" t="s">
         <v>729</v>
       </c>
-      <c r="F385" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6">
-      <c r="A386" t="s">
+      <c r="C388" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" t="s">
         <v>730</v>
       </c>
-      <c r="F386" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="387" spans="1:6">
-      <c r="A387" t="s">
+      <c r="C389" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" t="s">
         <v>731</v>
       </c>
-      <c r="F387" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="388" spans="1:6">
-      <c r="A388" t="s">
+      <c r="C390" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391" t="s">
         <v>732</v>
       </c>
-      <c r="F388" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="389" spans="1:6">
-      <c r="A389" t="s">
-        <v>733</v>
-      </c>
-      <c r="F389" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="390" spans="1:6">
-      <c r="A390" t="s">
-        <v>734</v>
-      </c>
-      <c r="F390" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="391" spans="1:6">
-      <c r="A391" t="s">
-        <v>735</v>
-      </c>
       <c r="B391" t="s">
-        <v>635</v>
-      </c>
-      <c r="F391" t="s">
-        <v>8</v>
+        <v>632</v>
+      </c>
+      <c r="C391" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/fr/CRSChannelCode.xlsx
+++ b/api/xlsx/fr/CRSChannelCode.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="735">
   <si>
     <t>code</t>
   </si>
@@ -1655,6 +1655,12 @@
   </si>
   <si>
     <t>Institut des Nations Unies pour la recherche sur le désarmement</t>
+  </si>
+  <si>
+    <t>41151</t>
+  </si>
+  <si>
+    <t>Centre international de recherche sur le cancer</t>
   </si>
   <si>
     <t>46027</t>
@@ -2544,7 +2550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C391"/>
+  <dimension ref="A1:C392"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5616,15 +5622,15 @@
       <c r="A284" t="s">
         <v>549</v>
       </c>
+      <c r="B284" t="s">
+        <v>550</v>
+      </c>
       <c r="C284" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>550</v>
-      </c>
-      <c r="B285" t="s">
         <v>551</v>
       </c>
       <c r="C285" t="s">
@@ -6042,15 +6048,15 @@
       <c r="A323" t="s">
         <v>626</v>
       </c>
+      <c r="B323" t="s">
+        <v>627</v>
+      </c>
       <c r="C323" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>627</v>
-      </c>
-      <c r="B324" t="s">
         <v>628</v>
       </c>
       <c r="C324" t="s">
@@ -6076,18 +6082,18 @@
         <v>632</v>
       </c>
       <c r="C326" t="s">
-        <v>633</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
+        <v>633</v>
+      </c>
+      <c r="B327" t="s">
         <v>634</v>
       </c>
-      <c r="B327" t="s">
+      <c r="C327" t="s">
         <v>635</v>
-      </c>
-      <c r="C327" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -6403,21 +6409,21 @@
         <v>692</v>
       </c>
       <c r="B356" t="s">
-        <v>632</v>
+        <v>693</v>
       </c>
       <c r="C356" t="s">
-        <v>633</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B357" t="s">
-        <v>694</v>
+        <v>634</v>
       </c>
       <c r="C357" t="s">
-        <v>5</v>
+        <v>635</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -6435,32 +6441,35 @@
       <c r="A359" t="s">
         <v>697</v>
       </c>
+      <c r="B359" t="s">
+        <v>698</v>
+      </c>
       <c r="C359" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>698</v>
-      </c>
-      <c r="B360" t="s">
         <v>699</v>
       </c>
       <c r="C360" t="s">
-        <v>633</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
         <v>700</v>
       </c>
+      <c r="B361" t="s">
+        <v>701</v>
+      </c>
       <c r="C361" t="s">
-        <v>5</v>
+        <v>635</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C362" t="s">
         <v>5</v>
@@ -6468,7 +6477,7 @@
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C363" t="s">
         <v>5</v>
@@ -6476,7 +6485,7 @@
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C364" t="s">
         <v>5</v>
@@ -6484,7 +6493,7 @@
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C365" t="s">
         <v>5</v>
@@ -6492,7 +6501,7 @@
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C366" t="s">
         <v>5</v>
@@ -6500,7 +6509,7 @@
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C367" t="s">
         <v>5</v>
@@ -6508,7 +6517,7 @@
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C368" t="s">
         <v>5</v>
@@ -6516,9 +6525,6 @@
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>708</v>
-      </c>
-      <c r="B369" t="s">
         <v>709</v>
       </c>
       <c r="C369" t="s">
@@ -6529,13 +6535,16 @@
       <c r="A370" t="s">
         <v>710</v>
       </c>
+      <c r="B370" t="s">
+        <v>711</v>
+      </c>
       <c r="C370" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C371" t="s">
         <v>5</v>
@@ -6543,7 +6552,7 @@
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C372" t="s">
         <v>5</v>
@@ -6551,7 +6560,7 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C373" t="s">
         <v>5</v>
@@ -6559,7 +6568,7 @@
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C374" t="s">
         <v>5</v>
@@ -6567,7 +6576,7 @@
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C375" t="s">
         <v>5</v>
@@ -6575,7 +6584,7 @@
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C376" t="s">
         <v>5</v>
@@ -6583,7 +6592,7 @@
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C377" t="s">
         <v>5</v>
@@ -6591,7 +6600,7 @@
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C378" t="s">
         <v>5</v>
@@ -6599,7 +6608,7 @@
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C379" t="s">
         <v>5</v>
@@ -6607,9 +6616,6 @@
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>720</v>
-      </c>
-      <c r="B380" t="s">
         <v>721</v>
       </c>
       <c r="C380" t="s">
@@ -6620,13 +6626,16 @@
       <c r="A381" t="s">
         <v>722</v>
       </c>
+      <c r="B381" t="s">
+        <v>723</v>
+      </c>
       <c r="C381" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C382" t="s">
         <v>5</v>
@@ -6634,7 +6643,7 @@
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C383" t="s">
         <v>5</v>
@@ -6642,7 +6651,7 @@
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C384" t="s">
         <v>5</v>
@@ -6650,7 +6659,7 @@
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C385" t="s">
         <v>5</v>
@@ -6658,7 +6667,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C386" t="s">
         <v>5</v>
@@ -6666,7 +6675,7 @@
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C387" t="s">
         <v>5</v>
@@ -6674,7 +6683,7 @@
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C388" t="s">
         <v>5</v>
@@ -6682,7 +6691,7 @@
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C389" t="s">
         <v>5</v>
@@ -6690,7 +6699,7 @@
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C390" t="s">
         <v>5</v>
@@ -6698,12 +6707,20 @@
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>732</v>
-      </c>
-      <c r="B391" t="s">
-        <v>632</v>
+        <v>733</v>
       </c>
       <c r="C391" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" t="s">
+        <v>734</v>
+      </c>
+      <c r="B392" t="s">
+        <v>634</v>
+      </c>
+      <c r="C392" t="s">
         <v>5</v>
       </c>
     </row>
